--- a/handoffs/goods-reconstruction/DCA_goods_reconstruction_RUN-receXkVSVZTfjD1j6_structured_output_2026-09-17.xlsx
+++ b/handoffs/goods-reconstruction/DCA_goods_reconstruction_RUN-receXkVSVZTfjD1j6_structured_output_2026-09-17.xlsx
@@ -2,15 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rb620507476ce4adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipments" sheetId="2" r:id="R4cbbb83898874773"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Van_Missions" sheetId="3" r:id="R7c0cfa785fbf4675"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pallets_declared" sheetId="4" r:id="R99c21278f3a44b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="5" r:id="Raf2fb5f65fe64d11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="6" r:id="R58f0bfa581024f9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_List" sheetId="7" r:id="Rb7737955281e4934"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="8" r:id="Rd8ac05ffa7d6451f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objects" sheetId="9" r:id="Ra6216262352344fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rd2618af030d540cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run_History" sheetId="2" r:id="R98e60e5bc4404f2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shipments" sheetId="3" r:id="R4e3998c48a57431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Van_Missions" sheetId="4" r:id="R90acf27f9c314d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pallets_declared" sheetId="5" r:id="R2796babe0a6440b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconciliation" sheetId="6" r:id="R7c5ebd551c1645d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage" sheetId="7" r:id="R6f6bccc40d7c48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review_List" sheetId="8" r:id="R9eaf5c8cbea840f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="9" r:id="R260ab3633b424273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objects" sheetId="10" r:id="R14eb160ae9e741ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="#,##0"/>
+  </x:numFmts>
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -58,8 +62,14 @@
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -76,6 +86,11 @@
         <x:fgColor rgb="FFD9D9D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDDDDD"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -83,7 +98,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -95,22 +110,39 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -404,17 +436,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" customWidth="1"/>
+    <x:col min="1" max="1" width="26" customWidth="1"/>
     <x:col min="2" max="2" width="120" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="inlineStr">
+      <x:c r="A1" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Item</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
+      <x:c r="B1" s="15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Value</x:t>
         </x:is>
@@ -428,94 +460,723 @@
       </x:c>
       <x:c r="B2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Inspectable structured output of RUN-receXkVSVZTfjD1j6 (DCA goods &amp; shipment history reconstruction). Detail is limited to what the processed sources state. This is a staging/review shape, NOT an adopted production schema.</x:t>
+          <x:t xml:space="preserve">Inspectable structured output of RUN-receXkVSVZTfjD1j6 (DCA goods &amp; shipment history reconstruction). Detail is limited to what the processed sources state. Staging/review shape, NOT an adopted production schema.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="3" ht="24" hidden="0" customHeight="1">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Status</x:t>
+          <x:t xml:space="preserve">Checkpoint</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>Interim 37-source snapshot from Claude’s initial pass, with claim corrections and PR export repair on 17 Sep 2026. Self-evaluation remains INSUFFICIENT. The Evidence tab indexes 53 records now linked to the run: 37 in this snapshot and 16 additional records awaiting incorporation. No human validation or valuation performed by this repair.</x:v>
+        <x:v>v6 consistency repair checkpoint 2026-09-17T19:42:35.495Z: 56 evidence records, 30 objects, 120 evidence links, 8 object relationships, 2 identified meetings. Original source excerpts and labelled historical corrections are preserved; the current fields and this export describe this checkpoint.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" hidden="0" customHeight="1">
       <x:c r="A4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Inclusion rule for totals</x:t>
+          <x:t xml:space="preserve">Status</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>Shipment kg follow the declared source totals. The kg_declared column does not imply that loose items are excluded: consult kg_loose_declared and the source, since March/May totals include loose items while July separates them. Van missions and undocumented trucks remain separate; no combined totals are produced.</x:v>
+        <x:v>Interim. Domain self-evaluation remains INSUFFICIENT: undocumented Jan–Feb trucks, unread sources and delivery-evidence gaps remain. Confirmed answers are preserved. May scope and Mission 36 total are owner-confirmed; calculated May totals and explanations are unreviewed interpretations. No valuation performed.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Exclusion rule</x:t>
+          <x:t xml:space="preserve">Inclusion rule for totals</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Nothing is summed across the Shipments tab and the Van_Missions tab; James's monthly totals are never added to declared totals. Duplicate copies of the same document (operational folder, manifest bundle, upload) count once.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">Shipment kg follow the declared source totals. kg_declared does not imply loose items are excluded: consult kg_loose_declared and the source (March/May totals include loose items; July separates them). Van missions and undocumented trucks stay separate; no combined totals are produced.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
       <x:c r="A6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Airtable trace</x:t>
+          <x:t xml:space="preserve">Event states</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="2" t="str">
-        <x:v>DCA Evidence &amp; Reconciliation, run RUN-receXkVSVZTfjD1j6. Objects and Evidence provide full Airtable record URLs; available original source URLs and references are in Evidence. URLs are stored as text for portable inspection. The index does not establish validation or full processing.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Planned unloading, reported unloading and documented receipt are different states. Processed sources report March bedding receipt, May unloading and August unloading second-hand. The cited June/July unloading messages establish plans; their completion remains unestablished. No consignee receipt document has been processed; absence elsewhere is not established.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
       <x:c r="A7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Source of numbers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Every number is taken from a source listed in the Evidence tab; column 'source_evidence' on each row names it. Numbers typed from Kees's notes are marked 'Kees note (16 Sep 2026)'.</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Validation scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>Owner validation is scoped to the exact claim. Kees confirmed May movement scope and accepted Mission 36 at 527 kg. The 10,737 kg May total, 380 kg difference and category mapping are derived. G-16/G-30 have unreviewed validation and pilot_system_interpretation; their proposed mechanism is unconfirmed and Q-D remains dropped.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Valuation</x:t>
+          <x:t xml:space="preserve">Airtable trace</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Deferred by instruction. Rates, prices and euro values appear only as attributed source claims where they were already in a source.</x:t>
+          <x:t xml:space="preserve">DCA Evidence &amp; Reconciliation, run RUN-receXkVSVZTfjD1j6. Objects and Evidence tabs carry full record URLs. IDs are trace keys, not reader citations.</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Correction pass</x:t>
+          <x:t xml:space="preserve">Source of numbers</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>17 Sep 2026: Claude corrected G-03/G-11 candidate identities, G-16/G-19 hypotheses, G-17’s 507/527 kg conflict, and G-27’s inspection scope; fixed five formula-saved notes. PR repair restores row/item/source alignment, neutral questions, qualified object labels and evidence navigation. Existing correction notes remain in Airtable.</x:v>
+        <x:v>Source values and references are retained per row. Derived totals and proposed interpretations are labelled separately from source statements and human confirmations. Evidence indexes source membership; it does not establish complete attachment processing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Valuation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Deferred by instruction. Rates/prices/euro values appear only as attributed source claims already present in a source.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Version</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>v6 — 17 Sep 2026, Codex consistency repair authorised by Anja. Current coverage/status fields and outputs aligned; source quantities and prior corrections preserved. Supersedes the inconsistent v5 export set.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" hidden="0" customHeight="1">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">History (labelled, not current)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>v1 initial pass → v2 claim corrections → v3 PR repair → v4 evidence incorporation → v5 owner-answer/access-history review → v6 consistency repair. Earlier versions mixed current and superseded assertions. Record counts and unresolved questions in those versions are historical; use the checkpoint and current Coverage/Review_List. Earlier 88 links was an unverified planning figure; verified sequence 84 → 104 → 118 → 120.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" customWidth="1"/>
+    <x:col min="2" max="2" width="60" customWidth="1"/>
+    <x:col min="3" max="3" width="54" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">object_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">display_name</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">airtable_object_url</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>validation_status</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>epistemic_status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec1A3tgId8npy6eE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>G-01 January truck (20 Jan 2026): 20 pallets / 10,036 kg declared; HW 14 / 7,403; NR 6 / 2,633</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec1A3tgId8npy6eE</x:v>
+      </x:c>
+      <x:c r="D2" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E2" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recclQ34CTtgzne9g</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>G-02 Correction: Kees's January food shortfall (−751 kg) is an artefact of unallocated 'split pending' weights, not a missing shipment</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recclQ34CTtgzne9g</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E3" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="48" hidden="0" customHeight="1">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="str">
+        <x:v>G-03 January pallets not on the January CMR: owner says 99% not repacked; weight+composition candidate matches suggest P12→Mar NR P1, P16→Mar NR P2, P18→Mar HW P26, P22→Mar P27/P28, P10→May P11; P27 weak (Aug P6); P4, P6, P8, P26 unmatched</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recQHyIOyozXotKBh</x:v>
+      </x:c>
+      <x:c r="D4" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E4" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recqfCoNgY3BgXINx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>G-04 Mission 33 (armoured van) load unresolved: pallet 18's 24 medical boxes (315 kg) are annotated 'in the van for mission 33' but an identical pallet appears on the March truck (HW P26); Kees recalls mostly second-hand clothing</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recqfCoNgY3BgXINx</x:v>
+      </x:c>
+      <x:c r="D5" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E5" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" hidden="0" customHeight="1">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-reckOFPCVHjlD6KJF</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>G-05 Mission 33 timing re-read: Bohdan received the armoured van in DECEMBER 2025 (Lieke's message lists it under December achievements); a second vehicle was not yet ready on 3 Feb; James's January 'Mission 33 armoured van delivery' label is therefore a period error or refers to something else — unresolved</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/reckOFPCVHjlD6KJF</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E6" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="48" hidden="0" customHeight="1">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec3LncyByihvWJ7w</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>G-06 Trucks without shipment sheets (Jan–Feb 2026): James lists Truck 1 (9 Jan), Truck 3 (28 Jan), Truck 4 (11 Feb) carrying 48,000 kg 'Medical'; Kees holds no documents (huddle-confirmed); Feb appeal says '5 trucks in 2026'; Lieke's 'three trucks' was about December 2025</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec3LncyByihvWJ7w</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recO2rSGDV2NHLlFu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>G-07 Contents of the undocumented Jan–Feb trucks are not established: 'mattresses' rests on Kees's belief and James's 'Medical' category; the winter appeal describes sleeping bags, duvets, bedding, winter clothing and food</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recO2rSGDV2NHLlFu</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec2SXYOAnOati9oQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>G-08 James's Kharkiv/Donetsk region split is a reporting convention, not a consignee split (NR clothing → Donetsk in Jan but Kharkiv in Mar; incontinence → Donetsk; Jan NR food 1,699 appears as 699)</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec2SXYOAnOati9oQ</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="str">
+        <x:v>operational_terminology</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" hidden="0" customHeight="1">
       <x:c r="A10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Version</x:t>
+          <x:t xml:space="preserve">ROB-recl6gIk4jwSbqm6p</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="2" t="str">
-        <x:v>v3 — PR repair, 17 Sep 2026. v1 is preserved in PR #42 commit df16b9c64362508aad001b7c6627290d5d095200. v2 was supplied as files.zip. Historical results remain the bounded 37-source snapshot; the 16 additional indexed records require reconciliation before the next research output.</x:v>
+        <x:v>G-09 March truck (10 Mar 2026): 31 pallets numbered 1–33 (22, 31 absent) / 19,319 kg; NR 7 / 4,226 incl. 134 loose items 244 kg; HW 24 / 15,093</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recl6gIk4jwSbqm6p</x:v>
+      </x:c>
+      <x:c r="D10" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" hidden="0" customHeight="1">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recWORLSXcsZPpKOQ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>G-10 March sheet internal inconsistencies: NR box summary 250 omits 92 nutrition boxes (itemised 342); HW summary 1,106 vs itemised 1,107; fractional weights show pro-rata splits of mixed pallets 15, 21, 25, 32</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recWORLSXcsZPpKOQ</x:v>
+      </x:c>
+      <x:c r="D11" s="18" t="str">
+        <x:v>unreviewed</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" hidden="0" customHeight="1">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec0W2XImFq9vN3CP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="str">
+        <x:v>G-11 February WhatsApp pallet notes: candidate matches to March pallets (#40↔P32; #39↔P15; #45↔P21 with a 14-vs-15 baby-box conflict; #44↔NR P30); #43 and one unnumbered H4U note unresolved; #35 supersedes #34</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec0W2XImFq9vN3CP</x:v>
+      </x:c>
+      <x:c r="D12" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" hidden="0" customHeight="1">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recB37f26Q14iwW6a</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="str">
+        <x:v>G-12 March H4U attribution (owner-confirmed): pallets 7, 8, 11, 15, 19 and 32 went to H4U on the March truck and no others (3,871 kg); which pallet note #43 denotes remains open</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recB37f26Q14iwW6a</x:v>
+      </x:c>
+      <x:c r="D13" s="18" t="str">
+        <x:v>owner_validated</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" hidden="0" customHeight="1">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recnh2w8NfAksexUL</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="str">
+        <x:v>G-13 Mission 34 (van, 8–21 Feb 2026): 13 Nutridrink boxes / 260 kg confirmed; short-expiry nutrition prioritised for the van, remainder held for the next truck</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recnh2w8NfAksexUL</x:v>
+      </x:c>
+      <x:c r="D14" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" hidden="0" customHeight="1">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recR0aCTKpJQY7a1T</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="str">
+        <x:v>G-14 Mission 35 (van, 6–17 Apr 2026): loading list 6 lines / 686 kg; James's tab titles it 'two ambulances delivery'; ~5 repaired ambulances were due to go to Ukraine end of March (one for Bogdan's team) — which were delivered, and whether vehicles count as goods, unresolved</x:v>
+      </x:c>
+      <x:c r="C15" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recR0aCTKpJQY7a1T</x:v>
+      </x:c>
+      <x:c r="D15" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" hidden="0" customHeight="1">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recQVOExvYChyUyHG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="str">
+        <x:v>G-15 May truck (6 May 2026): 20 pallets / 10,210 kg; HW 16 / 8,700 (pallets 1–4 annotated H4U Ludmila Zhytomir; 6 and 17 DCA James Kamyonka/Kramatorsk); NR 4 / 1,510; unloading at HW warehouses reported by 19 May</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recQVOExvYChyUyHG</x:v>
+      </x:c>
+      <x:c r="D16" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" hidden="0" customHeight="1">
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recFkYkFT1rMJPJ6n</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="str">
+        <x:v>G-16 May reporting: calculated 380 kg difference from the reconstructed total; proposed 572/503/192 explanation remains unconfirmed</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recFkYkFT1rMJPJ6n</x:v>
+      </x:c>
+      <x:c r="D17" s="18" t="str">
+        <x:v>unreviewed</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" hidden="0" customHeight="1">
+      <x:c r="A18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recjIzGNdwLJfju2W</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="2" t="str">
+        <x:v>G-17 Mission 36 (van, 24 May–7 Jun 2026): 7 lines / 64 units / 527 kg — owner confirms the line sum is correct and the note's stated 507 kg total is an error</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recjIzGNdwLJfju2W</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>owner_validated</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" hidden="0" customHeight="1">
+      <x:c r="A19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recOiUWgo6VxgCpGs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="2" t="str">
+        <x:v>G-18 June truck SHI-0002 (24 Jun 2026, Zhytomyr/Makariv): 437 boxes / 7,570.5 kg; HW CMR covered H4U goods with unloading intended in Zhytomyr (per James, 'Olga agreed'); Salim 3,632; Lifeline 193 incl. sweets intended for a New Time children's camp; split pallets SU-0011/0012</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recOiUWgo6VxgCpGs</x:v>
+      </x:c>
+      <x:c r="D19" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" hidden="0" customHeight="1">
+      <x:c r="A20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recefuxSdBFM8PkuY</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="2" t="str">
+        <x:v>G-19 Proposed correction: James's June total 7,718 exceeds the manifest 7,570.5 by 147.5, exactly reproduced if SU-0011's full 288 kg sits in Donetsk food (2,735 + 288 = 3,023) while its 148 kg monitors also appear in house goods 193 — James to confirm</x:v>
+      </x:c>
+      <x:c r="C20" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recefuxSdBFM8PkuY</x:v>
+      </x:c>
+      <x:c r="D20" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" hidden="0" customHeight="1">
+      <x:c r="A21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recizQEts3O2pYoJn</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
+        <x:v>G-20 June SHI-0002 handover: Makariv unloading by Vova was the PLAN (James, 23 Jun); completion not evidenced — 3 Jul message implies arrival and partial collection only; Lifeline CMR was to cover Lifeline and a New Time children's camp; Monitors-vs-TVs unresolved</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recizQEts3O2pYoJn</x:v>
+      </x:c>
+      <x:c r="D21" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="36" hidden="0" customHeight="1">
+      <x:c r="A22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec5K5YO2pTOqSbFb</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="2" t="str">
+        <x:v>G-21 July truck SHI-0001 (picked up 30 May, stored; dispatch 4 Jul 2026, Kharkiv): 15,260 kg + 510 kg loose (gross 15,770); HW 19 / 8,890; NR 13 / 6,370; unloadings PLANNED ~6–7 Jul — completion not evidenced</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec5K5YO2pTOqSbFb</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="36" hidden="0" customHeight="1">
+      <x:c r="A23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recDmbeTI4kj1LGMs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="2" t="str">
+        <x:v>G-22 'Mission 37' denotes the 4 July 2026 truck journey (drivers' trip) and was reused in camp fundraising; it is not a DCA van mission, which is why Kees's folder set has no Mission 37</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recDmbeTI4kj1LGMs</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="str">
+        <x:v>operational_terminology</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="36" hidden="0" customHeight="1">
+      <x:c r="A24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recctSkY9s9OWX9N2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="2" t="str">
+        <x:v>G-23 July and August trucks are absent from James's workbook because it is the half-yearly Jan–Jun report (owner-confirmed; both due in the year-end report); Kees's reconstruction separately understates July as '~9,300+ kg' vs declared 15,260 + 510 kg</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recctSkY9s9OWX9N2</x:v>
+      </x:c>
+      <x:c r="D24" s="18" t="str">
+        <x:v>owner_validated</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="str">
+        <x:v>uncertainty_visibility_gap</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" hidden="0" customHeight="1">
+      <x:c r="A25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recj1ALxy6QQ0ajdE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>G-24 Mission 38 (van, 11–21 Jul 2026, camp 13–17 Jul): 55 boxes medical food 510 kg + 2 boxes food 15 kg to Lighthouse Makariv (list sent to James 10 Jul)</x:v>
+      </x:c>
+      <x:c r="C25" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recj1ALxy6QQ0ajdE</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="36" hidden="0" customHeight="1">
+      <x:c r="A26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recIOT2vNEsqCjJFp</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="2" t="str">
+        <x:v>G-25 August truck SHI-0003: loaded and departed 21 Aug 2026 (Kharkiv; carrier Stichting Dopomoha, shared truck via Wilfred); 20 pallets / 813 boxes / 10,290 kg; border 23 Aug; unloading at both places reported 30 Aug (second-hand)</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recIOT2vNEsqCjJFp</x:v>
+      </x:c>
+      <x:c r="D26" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="24" hidden="0" customHeight="1">
+      <x:c r="A27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recFHukYf2JtvL0Ak</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>G-26 Mission 39 (van, 21 Aug–3 Sep 2026): loading list prepared for James 20 Aug: 8 lines / 167 units / 1,286 kg incl. row 6 (15 boxes medical, 155 kg) recipient TBD</x:v>
+      </x:c>
+      <x:c r="C27" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recFHukYf2JtvL0Ak</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="24" hidden="0" customHeight="1">
+      <x:c r="A28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recTCK3iNLxzUljHh</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="2" t="str">
+        <x:v>G-27 James's Total tab (Jan–Jun) does not equal its monthly tabs in the uploaded copy's extracted values: Clothing €37,593 vs 41,533; Baby €44,940 vs 45,360; kg totals reconcile</x:v>
+      </x:c>
+      <x:c r="C28" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recTCK3iNLxzUljHh</x:v>
+      </x:c>
+      <x:c r="D28" s="18" t="str">
+        <x:v>unreviewed</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" hidden="0" customHeight="1">
+      <x:c r="A29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recXJEqaQUWu2GHBi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>G-28 The sender address on shipment documents is DCA's registered NGO address (Meidoornweg Badhoevedorp Jan–May → Lutmanstraat Amsterdam Jun–Aug), not a warehouse location — owner-confirmed</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recXJEqaQUWu2GHBi</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>owner_validated</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="36" hidden="0" customHeight="1">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rece5DMBqpS6H0YZJ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="str">
+        <x:v>G-29 Warehouse stock on 2 Sep 2026 (Kees's 25 observations, approximate): incl. ~260 fire extinguishers, 3 pallets winter clothing, ~2 pallets medical nutrition, wheelchairs ~6, rollators ~15 — end-of-period context, no weights</x:v>
+      </x:c>
+      <x:c r="C30" s="2" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rece5DMBqpS6H0YZJ</x:v>
+      </x:c>
+      <x:c r="D30" s="18" t="str">
+        <x:v>needs_owner_validation</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="str">
+        <x:v>historical_observed_reported_reality</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="36" hidden="0" customHeight="1">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recH2pas3XuMv2XVy</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
+        <x:v>G-30 Corrected May 2026 figures: owner-confirmed inputs (scope; mission 36 = 527 kg), run-derived totals — truck 10,210 + van 527 = 10,737 kg; James's 11,117 overstates by 380 (mechanism of his figures remains a separate proposed reading, G-16)</x:v>
+      </x:c>
+      <x:c r="C31" s="2" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recH2pas3XuMv2XVy</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="str">
+        <x:v>unreviewed</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>pilot_system_interpretation</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -524,6 +1185,197 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" customWidth="1"/>
+    <x:col min="2" max="2" width="26" customWidth="1"/>
+    <x:col min="3" max="3" width="95" customWidth="1"/>
+    <x:col min="4" max="4" width="60" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phase</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">when</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">available / read / applied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">verifiable identifier</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" hidden="0" customHeight="1">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0 — before substantive work</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">16 Sep ~22:30–23:00 UTC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="str">
+        <x:v>Claude-reported history: read the goods prompt, Airtable Standard, three core skills and Drive method copies while repository requests returned 404 and staging 403. January/March analysis began with the gap declared. Codex did not independently replay those original runtime responses.</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>Reported original runtime evidence preserved in run notes; source access errors not independently reproduced in this repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1 — repo via project knowledge</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">17 Sep ~01:05 CEST</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="str">
+        <x:v>Claude reports that governing files became readable via project knowledge and that staging writes began after those reads. The route exposed no revision identifier. A read does not by itself establish that every rule was applied.</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">none — route exposes no revision identifier (unverifiable)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="48" hidden="0" customHeight="1">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2 — repository ZIPs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">in uploads 16 Sep 23:28 UTC; extracted/read at correction pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full method files readable offline; six review findings reassessed against them.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="str">
+        <x:v>Claude-reported ZIP-comment SHAs: dca-ai d131d8136eb2b98f4b4704958d00a1f9192f5d33; dca-architecture 985ff937627cae887671f7f2301f1bd48cdc5db0. Original archives were not independently inspected by Codex in this repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3 — PR #42</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">incorporation pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Repo public; branch files read in full (codeload tarball); 16 additional evidence records reconciled.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">commits df16b9c (handoff), 6c8541f (repair)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4 — review pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">17 Sep ~19:00 CEST</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full ZIP inspection (workflow §§9/11/16/21; tests; goods prompt); meaning corrections; owner answers; this export.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">this file's Checkpoint row</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unverifiable</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>Unknown: phase-1 revision; whether phase-0 Drive copies matched the governing revision; exact causes of earlier reasoning failures. Access, reading and demonstrated application are different. The mixed access history does not support a clean method test or a single root-cause conclusion.</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cause classification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="str">
+        <x:v>Observed defects include overstated identities, plans treated as completion, overbroad validation, an unchecked source sum and inconsistent exports. Available/read rules according to Claude constrain possible explanations but do not prove one root cause. Workflow §2 already separates plans from occurrence; that rule was not absent.</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="str">
+        <x:v>Codex checked the governing workflow at d131d813; examples/recovery/export checks are strengthened within the existing method.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
+      <x:c r="A9" s="18" t="str">
+        <x:v>5 — Codex consistency repair</x:v>
+      </x:c>
+      <x:c r="B9" s="18" t="str">
+        <x:v>Checkpoint 2026-09-17T19:42:35.495Z</x:v>
+      </x:c>
+      <x:c r="C9" s="18" t="str">
+        <x:v>Verified and corrected current staging summaries/statuses/coverage and generated v6. Confirmed answers and original excerpts retained. Regression specifications proposed in PR #42 are not executed runtime tests.</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str">
+        <x:v>PR #42 parent 6c8541f382b2d97725184c834178b78f2f98823d; current method files inspected against main 9b2335aecd354a17c50ec02066f1eced19f5b4d4; checkpoint in README.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -543,7 +1395,7 @@
     <x:col min="14" max="14" width="24" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" hidden="0" customHeight="1">
+    <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">shipment_ref</x:t>
@@ -584,8 +1436,10 @@
           <x:t xml:space="preserve">boxes_declared</x:t>
         </x:is>
       </x:c>
-      <x:c r="I1" s="1" t="str">
-        <x:v>kg_declared</x:v>
+      <x:c r="I1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kg_declared</x:t>
+        </x:is>
       </x:c>
       <x:c r="J1" s="1" t="inlineStr">
         <x:is>
@@ -1011,12 +1865,12 @@
       </x:c>
       <x:c r="L7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">declared; loaded/sent per Kees (prior run); delivery unverified</x:t>
+          <x:t xml:space="preserve">declared; loaded/sent per Kees (prior run); unloading at HW warehouses reported by James 19 May (second-hand); receipt documents not processed</x:t>
         </x:is>
       </x:c>
       <x:c r="M7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-recDe227kjiqwpZc5</x:t>
+          <x:t xml:space="preserve">EVD-recDe227kjiqwpZc5; EVD-recANxlI6i696JKG8</x:t>
         </x:is>
       </x:c>
       <x:c r="N7" s="2" t="inlineStr">
@@ -1072,17 +1926,17 @@
       </x:c>
       <x:c r="K8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HW SU-0001–0006 3,745.5; Salim 3,632; Lifeline 193; split pallets SU-0011/0012. AC7440HP/AC0450XG, driver Melnychuk Yaroslav. Lutmanstraat sender. Invoice 'truck loaded 24 June' to Finance 6 Jul.</x:t>
+          <x:t xml:space="preserve">HW SU-0001–0006 3,745.5; Salim 3,632; Lifeline 193; split pallets SU-0011/0012. AC7440HP/AC0450XG, driver Melnychuk Yaroslav. Lutmanstraat sender. Invoice 'truck loaded 24 June' to Finance 6 Jul. Per James (DM 23 Jun): HW CMR (place of delivery Zhytomyr) carried H4U goods; Lifeline CMR covered Lifeline (monitors/'TVs', naming unresolved) and sweets for a New Time children's camp; Makariv consignments to be unloaded by Vova (instruction; completion not evidenced).</x:t>
         </x:is>
       </x:c>
       <x:c r="L8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">declared; loaded 24 Jun (invoice email); 3 Jul not all recipients had collected</x:t>
+          <x:t xml:space="preserve">declared; loaded 24 Jun (invoice email); Zhytomyr/Makariv unloadings PLANNED per James's 23 Jun instruction — completion not evidenced; 3 Jul: not all recipients had collected goods</x:t>
         </x:is>
       </x:c>
       <x:c r="M8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-recjovJhHNHrkGZb3; EVD-recibLdWHNIJanw5J; EVD-recJI4FH0GVHLhByd</x:t>
+          <x:t xml:space="preserve">EVD-recjovJhHNHrkGZb3; EVD-recibLdWHNIJanw5J; EVD-recJI4FH0GVHLhByd; EVD-recN9cYuabcVyjTpP; EVD-reclmhgQ3jzfn9gU2; EVD-recixLbfaLKkFOS01; EVD-recF6Tt5AAd4wB5E5</x:t>
         </x:is>
       </x:c>
       <x:c r="N8" s="2" t="inlineStr">
@@ -1136,17 +1990,17 @@
       </x:c>
       <x:c r="K9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HW 19 / 8,890 + 51 bags bedding 510 loose; NR 13 / 6,370. W.B. van der Donk, OL-78-FB, CMR 1/260704 &amp; 2/260704. Departed Sat 4 Jul 08:00; Polish road inspection en route.</x:t>
+          <x:t xml:space="preserve">HW 19 / 8,890 + 51 bags bedding 510 loose; NR 13 / 6,370. W.B. van der Donk, OL-78-FB, CMR 1/260704 &amp; 2/260704. Departed Sat 4 Jul 08:00; Polish road inspection en route. Goods picked up Sat 30 May and stored by Enrico/Pete until dispatch (legacy Airtable record) — pickup date explained. Gross incl. loose 15,770 kg (box-level extract).</x:t>
         </x:is>
       </x:c>
       <x:c r="L9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">declared; departure evidenced (Slack); delivery unverified</x:t>
+          <x:t xml:space="preserve">declared; departure 4 Jul evidenced (Slack); unloadings at both Kharkiv consignees PLANNED ~6–7 Jul (forward-looking messages) — completion not evidenced; receipt documents not processed</x:t>
         </x:is>
       </x:c>
       <x:c r="M9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-rec3AuCzNvlH0aA5H; EVD-reccKtLmFYdcbgiig; EVD-recZJ8yS3SefenE0j; EVD-recOX5n0nZClxgYdP</x:t>
+          <x:t xml:space="preserve">EVD-rec3AuCzNvlH0aA5H; EVD-reccKtLmFYdcbgiig; EVD-recZJ8yS3SefenE0j; EVD-recOX5n0nZClxgYdP; EVD-rec7gntN5pp4IKN6R; EVD-recqqvvob4zYQpR8V; EVD-recrxfCCX5DKZ9SvY</x:t>
         </x:is>
       </x:c>
       <x:c r="N9" s="2" t="inlineStr">
@@ -1168,7 +2022,7 @@
       </x:c>
       <x:c r="C10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">2026-08-20 (list date; departure not established)</x:t>
+          <x:t xml:space="preserve">2026-08-21 (loaded and departed; list dated 20 Aug)</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" s="2" t="inlineStr">
@@ -1202,17 +2056,17 @@
       </x:c>
       <x:c r="K10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">HW 15 / 8,779; NR 5 / 1,511 hospital supplies. DAF XF AI8800HM/AA7888XS, driver Novitskyi Vladyslav. Stamped CMRs for carrier's bank 17–18 Aug.</x:t>
+          <x:t xml:space="preserve">HW 15 / 8,779; NR 5 / 1,511 hospital supplies. DAF XF AI8800HM/AA7888XS, driver Novitskyi Vladyslav. Stamped CMRs for carrier's bank 17–18 Aug. Carrier Stichting Dopomoha (DAF XF AI8800HM + Schmitz trailer AA7888XS); shared truck arranged via Wilfred (€4,600 quote, DCA ≈ €2,800 for ~20 pallets); H4U drop-off before Kyiv discussed; onward drop-offs/end recipients deliberately kept off paper. Border 23 Aug; planned unloading Zhytomyr 25 / Kharkiv 26 Aug.</x:t>
         </x:is>
       </x:c>
       <x:c r="L10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">declared; paperwork evidenced; departure/delivery unverified</x:t>
+          <x:t xml:space="preserve">declared; departure 21 Aug evidenced (Kees, #logistics); unloading at both places reported by Bas 30 Aug (second-hand, source unstated); receipt documents not processed</x:t>
         </x:is>
       </x:c>
       <x:c r="M10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-rec0F392MGFzyMkvY; EVD-recx7hibtO7QmFOev</x:t>
+          <x:t xml:space="preserve">EVD-rec0F392MGFzyMkvY; EVD-recx7hibtO7QmFOev; EVD-recC9dOzCgXbRSQEm; EVD-recHgOgGg8Rdr638M; EVD-recil3LS2XJuZl9kZ; EVD-recUadXZjYAGon1Bt; EVD-recdDE2xp8ht4aJ8R</x:t>
         </x:is>
       </x:c>
       <x:c r="N10" s="2" t="inlineStr">
@@ -1226,7 +2080,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -1294,7 +2148,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="48" hidden="0" customHeight="1">
       <x:c r="A2" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mission 33</x:t>
@@ -1305,15 +2159,11 @@
           <x:t xml:space="preserve">Jan/Feb 2026 (date unresolved)</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">armoured van</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bohdan (van recipient per Lieke); onward unknown</x:t>
-        </x:is>
+      <x:c r="C2" s="2" t="str">
+        <x:v>van / armoured-van reporting label unresolved</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="str">
+        <x:v>Bohdan is the reported December van recipient; Mission 33 goods recipients remain unresolved.</x:v>
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
         <x:is>
@@ -1327,7 +2177,7 @@
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Jan working sheet: pallet 18 (24 boxes medical supplies, 315 kg) 'in the van for mission 33'. Kees recollection: mostly second-hand clothing ~700 kg (James). No loading list.</x:t>
+          <x:t xml:space="preserve">Jan working sheet: pallet 18 (24 boxes medical supplies, 315 kg) 'in the van for mission 33' — but an identical pallet appears on the March truck (HW P26), so this may be an unexecuted intention. Kees recollection: mostly second-hand clothing ~700 kg (James). The armoured van itself was received by Bohdan in DECEMBER 2025 (Lieke). No loading list.</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" s="2" t="inlineStr">
@@ -1337,7 +2187,7 @@
       </x:c>
       <x:c r="I2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-recpYmNnGlJCfftyh; EVD-reczExBGAKskkWAOy; EVD-recT9nVfjN2snhuCi; EVD-recNRAElLXonh6n4A</x:t>
+          <x:t xml:space="preserve">EVD-recpYmNnGlJCfftyh; EVD-reczExBGAKskkWAOy; EVD-recT9nVfjN2snhuCi; EVD-recNRAElLXonh6n4A; EVD-recuxxn3mlOO1aDUI</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" s="2" t="inlineStr">
@@ -1423,7 +2273,7 @@
       </x:c>
       <x:c r="G4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">13 food 253; 17 small food/bars 24; 1 mobility scooter 97; 16 expired medical supplies 128; 12 medical nutrition 154; 2 clothing 30. James tab: 630 kg, 'two ambulances delivery' (no figures).</x:t>
+          <x:t xml:space="preserve">13 food 253; 17 small food/bars 24; 1 mobility scooter 97; 16 expired medical supplies 128; 12 medical nutrition 154; 2 clothing 30. James tab: 630 kg, 'two ambulances delivery' (no figures). Context: ~5 repaired ambulances due to go end of March, one for Bogdan's team (#marketing, Mar).</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" s="2" t="inlineStr">
@@ -1433,7 +2283,7 @@
       </x:c>
       <x:c r="I4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-recDpcZyE0q3nqz4p; EVD-reclaxOv0x7yGfjXB</x:t>
+          <x:t xml:space="preserve">EVD-recDpcZyE0q3nqz4p; EVD-reclaxOv0x7yGfjXB; EVD-recoHTWw0w5oqPDCT</x:t>
         </x:is>
       </x:c>
       <x:c r="J4" s="2" t="inlineStr">
@@ -1442,7 +2292,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" hidden="0" customHeight="1">
+    <x:row r="5" ht="48" hidden="0" customHeight="1">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mission 36</x:t>
@@ -1466,20 +2316,18 @@
       <x:c r="E5" s="2" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="F5" s="2" t="n">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="G5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Food 23/245; med nutrition 14/112; med nutrition accessories 5/20; medical accessories (evac) 2/10; fire extinguishers 15/90; clothing 4/40; evacuation chair 1/10. NOTE: stated total 507 kg conflicts with line sum 527 kg (source-internal, unresolved).</x:t>
-        </x:is>
+      <x:c r="F5" s="19" t="n">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="G5" s="2" t="str">
+        <x:v>Food 23/245; med nutrition 14/112; med nutrition accessories 5/20; medical accessories (evac) 2/10; fire extinguishers 15/90; clothing 4/40; evacuation chair 1/10. Original note stated 507 kg; listed weights sum to 527 kg. Kees accepted 527 kg in his 17 Sep comment; the original source discrepancy remains in the lineage.</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
-        <x:v>source conflict: 507 kg stated / 527 kg line sum; unresolved</x:v>
+        <x:v>owner_validated: 527 kg accepted; original stated 507 kg retained as source history</x:v>
       </x:c>
       <x:c r="I5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EVD-recRp4HzSsJj4FwZ5</x:t>
+          <x:t xml:space="preserve">EVD-recRp4HzSsJj4FwZ5; EVD-recsbIRbOrDpPwwWa</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" s="2" t="inlineStr">
@@ -1641,7 +2489,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -2735,7 +3583,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="26" ht="24" hidden="0" customHeight="1">
+    <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TRK-2026-03-10</x:t>
@@ -2767,8 +3615,10 @@
           <x:t xml:space="preserve">Incontinence 24</x:t>
         </x:is>
       </x:c>
-      <x:c r="H26" s="2" t="str">
-        <x:v>Candidate match to January P22: same 24 incontinence boxes, 276 kg here vs 275 kg in January. P27 is another candidate; identity unresolved.</x:v>
+      <x:c r="H26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Candidate match to January P22: same 24 incontinence boxes, 276 kg here vs 275 kg in January. P27 is another candidate; identity unresolved.</x:t>
+        </x:is>
       </x:c>
       <x:c r="I26" s="2" t="inlineStr">
         <x:is>
@@ -2819,7 +3669,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="28" ht="24" hidden="0" customHeight="1">
+    <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TRK-2026-03-10</x:t>
@@ -2851,8 +3701,10 @@
           <x:t xml:space="preserve">Clothing 24</x:t>
         </x:is>
       </x:c>
-      <x:c r="H28" s="2" t="str">
-        <x:v>Candidate match to WhatsApp #44: 24 winter-clothing boxes; identity unconfirmed.</x:v>
+      <x:c r="H28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Candidate match to WhatsApp #44: 24 winter-clothing boxes; identity unconfirmed.</x:t>
+        </x:is>
       </x:c>
       <x:c r="I28" s="2" t="inlineStr">
         <x:is>
@@ -3419,7 +4271,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="42" ht="24" hidden="0" customHeight="1">
+    <x:row r="42" ht="24" customHeight="1">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TRK-2026-03-10</x:t>
@@ -3451,8 +4303,10 @@
           <x:t xml:space="preserve">Food 45 + Baby 14 (sheet) vs 15 (WhatsApp #45) — conflict unresolved</x:t>
         </x:is>
       </x:c>
-      <x:c r="H42" s="2" t="str">
-        <x:v>Candidate match to WhatsApp #45: 45 Schoolfruit + 2 baby products + 13 wipes = 60. Sheet has 14 baby boxes and 59 itemised; unresolved.</x:v>
+      <x:c r="H42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Candidate match to WhatsApp #45: 45 Schoolfruit + 2 baby products + 13 wipes = 60. Sheet has 14 baby boxes and 59 itemised; unresolved.</x:t>
+        </x:is>
       </x:c>
       <x:c r="I42" s="2" t="inlineStr">
         <x:is>
@@ -3761,7 +4615,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="50" ht="24" hidden="0" customHeight="1">
+    <x:row r="50" ht="24" customHeight="1">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TRK-2026-03-10</x:t>
@@ -3793,8 +4647,10 @@
           <x:t xml:space="preserve">Food 34 + Hygiene 2</x:t>
         </x:is>
       </x:c>
-      <x:c r="H50" s="2" t="str">
-        <x:v>Candidate match to WhatsApp #39 (H4U): 18 animal + 2 hygiene + 16 hero boxes; identity unconfirmed.</x:v>
+      <x:c r="H50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Candidate match to WhatsApp #39 (H4U): 18 animal + 2 hygiene + 16 hero boxes; identity unconfirmed.</x:t>
+        </x:is>
       </x:c>
       <x:c r="I50" s="2" t="inlineStr">
         <x:is>
@@ -3845,7 +4701,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="52" ht="24" hidden="0" customHeight="1">
+    <x:row r="52" ht="36" hidden="0" customHeight="1">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">TRK-2026-03-10</x:t>
@@ -3878,7 +4734,7 @@
         </x:is>
       </x:c>
       <x:c r="H52" s="2" t="str">
-        <x:v>Candidate match to WhatsApp #40: 32 baby + 4 hygiene boxes; identity and H4U attribution require evidence review.</x:v>
+        <x:v>Candidate match to WhatsApp #40: 32 baby + 4 hygiene boxes; note identity remains unconfirmed. Separately, Kees confirmed March P32 belongs to the H4U set.</x:v>
       </x:c>
       <x:c r="I52" s="2" t="inlineStr">
         <x:is>
@@ -7763,7 +8619,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
@@ -8005,7 +8861,7 @@
       </x:c>
       <x:c r="D6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Working sheet: pallet 18 medical supplies 24 boxes 315 kg 'in the van for mission 33'; Lieke 23 Jan 'preparing mission 33'; James 3 Feb van not ready</x:t>
+          <x:t xml:space="preserve">Working sheet: pallet 18 (medical 24 boxes 315 kg) 'in the van for mission 33', but an identical pallet appears on the March truck (HW P26); Lieke's message places Bohdan's armoured-van receipt in DECEMBER 2025; James 3 Feb: a second vehicle not yet ready</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" s="2" t="inlineStr">
@@ -8015,12 +8871,12 @@
       </x:c>
       <x:c r="F6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Load and date both unresolved; James's Jan placement contradicted</x:t>
+          <x:t xml:space="preserve">Van receipt = Dec 2025; James's January 'armoured van delivery' label a period error or a different event; van load doubtful</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">UNRESOLVED</x:t>
+          <x:t xml:space="preserve">UNRESOLVED — narrowed (James)</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" s="2" t="inlineStr">
@@ -8155,7 +9011,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mar</x:t>
@@ -8181,11 +9037,15 @@
           <x:t xml:space="preserve">Truck March (def.) NR sheet</x:t>
         </x:is>
       </x:c>
-      <x:c r="F10" s="2" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="str">
-        <x:v>RETAINED</x:v>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RETAINED</x:t>
+        </x:is>
       </x:c>
       <x:c r="H10" s="2" t="inlineStr">
         <x:is>
@@ -8193,7 +9053,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="11" ht="36" hidden="0" customHeight="1">
+    <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mar</x:t>
@@ -8209,19 +9069,25 @@
           <x:t xml:space="preserve">Kees Correction #8: 59 itemised</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" s="2" t="str">
-        <x:v>Sheet: 45 food + 14 baby = 59 itemised, against 60 boxes stated. Candidate WhatsApp note #45: 45 + 2 + 13 = 60, implying 15 baby boxes if the match is correct.</x:v>
+      <x:c r="D11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sheet: 45 food + 14 baby = 59 itemised, against 60 boxes stated. Candidate WhatsApp note #45: 45 + 2 + 13 = 60, implying 15 baby boxes if the match is correct.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Screenshot 3/3; Truck March (def.)</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" s="2" t="str">
-        <x:v>Candidate note-to-pallet identity and 14-vs-15 box conflict unresolved; neither source silently corrected.</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="str">
-        <x:v>CANDIDATE MATCH + UNRESOLVED CONFLICT</x:v>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Candidate note-to-pallet identity and 14-vs-15 box conflict unresolved; neither source silently corrected.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CANDIDATE MATCH + UNRESOLVED CONFLICT</x:t>
+        </x:is>
       </x:c>
       <x:c r="H11" s="2" t="inlineStr">
         <x:is>
@@ -8229,7 +9095,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="12" ht="24" hidden="0" customHeight="1">
+    <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mar</x:t>
@@ -8240,28 +9106,38 @@
           <x:t xml:space="preserve">H4U pallets 7,8,11,15,19,32</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" s="2" t="str">
-        <x:v>Kees: from H4U tab</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="str">
-        <x:v>WhatsApp #39/#40 provide candidate content matches to P15/P32. Their identity is unconfirmed. P7/8/11/19 remain unverified; note #43 is unplaced.</x:v>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees: from H4U tab</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Owner comment 17 Sep: '7 + 8 + 11 + 15 + 19 + 32 went to H4U in march truck. Nothing more.' Set closed; combined 3,871 kg. Which pallet WhatsApp note #43 denotes remains open (G-11).</x:t>
+        </x:is>
       </x:c>
       <x:c r="E12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Screenshots; Truck March (def.)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="2" t="str">
-        <x:v>H4U planning tab absent from the original snapshot. G-12 still needs alignment with corrected G-11 in staging.</x:v>
-      </x:c>
-      <x:c r="G12" s="2" t="str">
-        <x:v>QUALIFICATION — candidate attribution</x:v>
-      </x:c>
-      <x:c r="H12" s="2" t="str">
-        <x:v>ROB-recB37f26Q14iwW6a; ROB-rec0W2XImFq9vN3CP</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa; Truck March (def.); screenshots</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">H4U planning tab no longer needed for the attribution</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RESOLVED — owner_validated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recB37f26Q14iwW6a; ROB-rec0W2XImFq9vN3CP</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mar</x:t>
@@ -8272,22 +9148,30 @@
           <x:t xml:space="preserve">Pallet 505 kg (NR P1) split 404/101</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" s="2" t="str">
-        <x:v>Kees Open_Items: hand-split</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="str">
-        <x:v>January working-sheet P12 and March NR P1 share 48 food + 8 clothing boxes and 505 kg. Carry-over is a candidate explanation; physical identity is unconfirmed.</x:v>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees Open_Items: hand-split</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">January working-sheet P12 and March NR P1 share 48 food + 8 clothing boxes and 505 kg. Carry-over is a candidate explanation; physical identity is unconfirmed.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Truck January xlsx; Truck March (def.)</x:t>
         </x:is>
       </x:c>
-      <x:c r="F13" s="2" t="str">
-        <x:v>Composition/weight similarity supports a candidate match; the 404/101 allocation remains an assumption.</x:v>
-      </x:c>
-      <x:c r="G13" s="2" t="str">
-        <x:v>CANDIDATE MATCH (unconfirmed)</x:v>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Composition/weight similarity supports a candidate match; the 404/101 allocation remains an assumption.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CANDIDATE MATCH (unconfirmed)</x:t>
+        </x:is>
       </x:c>
       <x:c r="H13" s="2" t="inlineStr">
         <x:is>
@@ -8295,7 +9179,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="14" ht="24" hidden="0" customHeight="1">
+    <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Mar</x:t>
@@ -8311,8 +9195,10 @@
           <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="2" t="str">
-        <x:v>January working-sheet P22 (24 incontinence boxes, 275 kg) is a candidate match to March P27 (275 kg) or P28 (276 kg). Identity unresolved.</x:v>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">January working-sheet P22 (24 incontinence boxes, 275 kg) is a candidate match to March P27 (275 kg) or P28 (276 kg). Identity unresolved.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E14" s="2" t="inlineStr">
         <x:is>
@@ -8324,8 +9210,10 @@
           <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
-      <x:c r="G14" s="2" t="str">
-        <x:v>CANDIDATE MATCH (unconfirmed)</x:v>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CANDIDATE MATCH (unconfirmed)</x:t>
+        </x:is>
       </x:c>
       <x:c r="H14" s="2" t="inlineStr">
         <x:is>
@@ -8417,7 +9305,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" hidden="0" customHeight="1">
+    <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">May</x:t>
@@ -8428,22 +9316,30 @@
           <x:t xml:space="preserve">Loose bedding 50×6=300</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" s="2" t="str">
-        <x:v>Kees Correction #6</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="str">
-        <x:v>Sheet says '6'; category total implies 300 kg for 50 loose items. Preserve the source entry and inferred total separately.</x:v>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees Correction #6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sheet says '6'; category total implies 300 kg for 50 loose items. Preserve the source entry and inferred total separately.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Def. Truck May</x:t>
         </x:is>
       </x:c>
-      <x:c r="F17" s="2" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G17" s="2" t="str">
-        <x:v>RETAINED — source interpretation</x:v>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RETAINED — source interpretation</x:t>
+        </x:is>
       </x:c>
       <x:c r="H17" s="2" t="inlineStr">
         <x:is>
@@ -8451,69 +9347,77 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="18" ht="24" hidden="0" customHeight="1">
+    <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">May</x:t>
         </x:is>
       </x:c>
-      <x:c r="B18" s="2" t="str">
-        <x:v>May P11 / January P10 carry-over candidate</x:v>
-      </x:c>
-      <x:c r="C18" s="2" t="str">
-        <x:v>Kees Correction #12</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="str">
-        <x:v>January P10 and May P11 both state 20 baby boxes / 342 kg. Candidate carry-over match; physical identity unconfirmed in corrected G-03.</x:v>
+      <x:c r="B18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">May P11 / January P10 carry-over candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees Correction #12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Owner: '99% sure they have not been repacked.' Weight+composition search across all 121 later pallets: P12→Mar NR P1, P16→Mar NR P2, P18→Mar HW P26, P22→Mar P27/P28, P10→May P11 (all exact); P27→Aug P6 weight-only; P4/P6/P8/P26 unmatched.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Truck January xlsx; Def. Truck May</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="2" t="str">
-        <x:v>Inspect Kees Correction #12 and any existing validation before asking again.</x:v>
-      </x:c>
-      <x:c r="G18" s="2" t="str">
-        <x:v>CANDIDATE MATCH (unconfirmed)</x:v>
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa; Truck January xlsx; later shipment documents</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Individual identities remain unconfirmed; P18 cuts across Mission 33 (G-04)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CANDIDATE MATCHES strengthened (owner 99%); identities unconfirmed</x:t>
+        </x:is>
       </x:c>
       <x:c r="H18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="36" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh; ROB-recqfCoNgY3BgXINx</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="60" hidden="0" customHeight="1">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">May</x:t>
         </x:is>
       </x:c>
-      <x:c r="B19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">James Baby 947 vs Kees 1,450 (+503)</x:t>
-        </x:is>
+      <x:c r="B19" s="2" t="str">
+        <x:v>May comparison and proposed calculation mechanism</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>Kees Comparison</x:v>
+        <x:v>Kees Comparison: Baby 1,450 vs James 947 (+503); James May total 11,117 kg. Kees later confirmed movement scope and instructed reconstruction.</x:v>
       </x:c>
       <x:c r="D19" s="2" t="str">
-        <x:v>Proposed reading: NR hygiene 572 kg may appear both within Kharkiv medical 1,510 and as Donetsk hygiene 572. HW incontinence 503 kg has no visible line. James’s calculation method is unconfirmed.</x:v>
+        <x:v>DERIVED: truck 10,210 + accepted van total 527 = 10,737 kg, 380 below James. PROPOSED EXPLANATION: NR hygiene 572 may be duplicated; HW incontinence 503 may sit inside Donetsk medical 553; approximately 192 kg of van items may be absent. Compatible arithmetic does not establish the mechanism or exclude other allocations.</x:v>
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Def. Truck May; James workbook</x:t>
+          <x:t xml:space="preserve">Def. Truck May; Kees note M36; EVD-rectVzwompdkoWvb5; James workbook</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="str">
-        <x:v>Possible duplication/omission is an interpretation of the totals; alternative constructions remain possible.</x:v>
+        <x:v>Confirmed inputs remain settled; totals and explanation are not separately owner-validated. Q-D remains dropped at Kees’s instruction.</x:v>
       </x:c>
       <x:c r="G19" s="2" t="str">
-        <x:v>PROPOSED READING — unconfirmed</x:v>
+        <x:v>DERIVED COMPARISON; PROPOSED MECHANISM — unreviewed</x:v>
       </x:c>
       <x:c r="H19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recFkYkFT1rMJPJ6n</x:t>
+          <x:t xml:space="preserve">ROB-recFkYkFT1rMJPJ6n; ROB-recH2pas3XuMv2XVy</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -8530,17 +9434,17 @@
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees note: 'Total as stated: 64 units — 507 kg'</x:t>
+          <x:t xml:space="preserve">Kees note stated total: 64 units — 507 kg (line sum 527)</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Seven line weights sum to 527 kg (245+112+20+10+90+40+10); units sum to 64 as stated. 20 kg source-internal discrepancy.</x:t>
+          <x:t xml:space="preserve">Owner comment 17 Sep: 'If the total sum = 527 kg, this is the correct one.' 527 kg is the accepted total; the note's stated 507 is the error (both preserved).</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees note</x:t>
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa; Kees note</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
@@ -8550,7 +9454,7 @@
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">UNRESOLVED — Kees to confirm which figure</x:t>
+          <x:t xml:space="preserve">RESOLVED — owner_validated (527)</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" s="2" t="inlineStr">
@@ -8559,7 +9463,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="21" ht="36" hidden="0" customHeight="1">
+    <x:row r="21" ht="36" customHeight="1">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Jun</x:t>
@@ -8575,19 +9479,25 @@
           <x:t xml:space="preserve">Kees: suspected duplicate 148 kg SU-0011 Lifeline</x:t>
         </x:is>
       </x:c>
-      <x:c r="D21" s="2" t="str">
-        <x:v>Proposed explanation: 2,735 + 288 = 3,023 reproduces Donetsk food, while 148 kg monitors also occur inside Lifeline 193. This is compatible with duplication; James’s calculation method is unconfirmed.</x:v>
+      <x:c r="D21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Proposed explanation: 2,735 + 288 = 3,023 reproduces Donetsk food, while 148 kg monitors also occur inside Lifeline 193. This is compatible with duplication; James’s calculation method is unconfirmed.</x:t>
+        </x:is>
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Manifest SHI-0002 Total; James workbook</x:t>
         </x:is>
       </x:c>
-      <x:c r="F21" s="2" t="str">
-        <x:v>Observed difference is 147.5 kg; the 148 kg duplication hypothesis also involves the 0.5 kg subtotal difference.</x:v>
-      </x:c>
-      <x:c r="G21" s="2" t="str">
-        <x:v>PROPOSED READING — unconfirmed</x:v>
+      <x:c r="F21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Observed difference is 147.5 kg; the 148 kg duplication hypothesis also involves the 0.5 kg subtotal difference.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PROPOSED READING — unconfirmed</x:t>
+        </x:is>
       </x:c>
       <x:c r="H21" s="2" t="inlineStr">
         <x:is>
@@ -8679,7 +9589,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="48" hidden="0" customHeight="1">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Jul</x:t>
@@ -8697,7 +9607,7 @@
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Declared 15,260 kg palletised + 510 loose; dispatched 4 Jul</x:t>
+          <x:t xml:space="preserve">Declared 15,260 kg palletised + 510 loose; dispatched 4 Jul; pickup 30 May explained (goods stored by carrier until 4 Jul dispatch); gross incl. loose 15,770 kg; unloadings PLANNED ~6–7 Jul (forward-looking messages) — completion not evidenced</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
@@ -8707,13 +9617,11 @@
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees understated; James not yet reported</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G24" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CORRECTION to Kees; ADDITION vs James</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Kees understated; Jul/Aug outside the half-yearly workbook by design (owner comment)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="2" t="str">
+        <x:v>CORRECTION to Kees; outside James’s Jan–Jun report by design</x:v>
       </x:c>
       <x:c r="H24" s="2" t="inlineStr">
         <x:is>
@@ -8805,7 +9713,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="48" hidden="0" customHeight="1">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Aug</x:t>
@@ -8821,25 +9729,19 @@
           <x:t xml:space="preserve">Kees: not in reconstruction (title Jan–Jun); James: zero</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Declared 10,290 kg (HW 8,779; NR 1,511); list 20 Aug; CMR stamping 14–18 Aug</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Loading list; Gmail 19ef5524fa59492e</x:t>
-        </x:is>
+      <x:c r="D27" s="2" t="str">
+        <x:v>Kees reported loading/departure on 21 Aug; border reported 23 Aug; Bas reported unloading at both places on 30 Aug, second-hand with original source unstated. Carrier Stichting Dopomoha, shared truck via Wilfred. Message posting time is not a precise departure time.</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="str">
+        <x:v>EVD-recC9dOzCgXbRSQEm; EVD-recHgOgGg8Rdr638M; loading-list and carrier evidence</x:v>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Departure date not established</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ADDITION</x:t>
-        </x:is>
+          <x:t xml:space="preserve">Departure question resolved by run evidence; unloading remains a second-hand report</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="str">
+        <x:v>ADDITION — departure reported; unloading is a second-hand report; no receipt processed</x:v>
       </x:c>
       <x:c r="H27" s="2" t="inlineStr">
         <x:is>
@@ -8949,318 +9851,398 @@
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Meidoornweg (Jan–May) → Lutmanstraat (Jun–Aug)</x:t>
+          <x:t xml:space="preserve">Owner comment 17 Sep: address where the NGO is registered, NOT the warehouse. Meidoornweg (Jan–May) → Lutmanstraat (Jun–Aug) is a registered-address change; never read it as a storage/loading location (loading place stated separately: Noordwijkerhout).</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">All truck documents</x:t>
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa; all truck documents</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Cause not established</x:t>
+          <x:t xml:space="preserve">Reason/date of the registration change itself: separate, not asked</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">RESOLVED — owner_validated (meaning)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recXJEqaQUWu2GHBi</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">May</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unloading of the May truck</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James (#logistics 19 May): unloading at HW warehouses; pallet 6 (Kamyonka) broken but dry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recANxlI6i696JKG8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="2" t="str">
+        <x:v>Second-hand report; no receipt document processed</x:v>
+      </x:c>
+      <x:c r="G31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADDITION (reported, unconfirmed)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recQVOExvYChyUyHG</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Jun</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">June HW consignment and end recipients</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees workbook: consignees HW/Salim/Lifeline</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James (DM 23 Jun, before loading): HW CMR (Zhytomyr) carried H4U goods, unloading intended in Zhytomyr ('Olga agreed'); Lifeline CMR to cover Lifeline and a New Time children's camp (sweets); Makariv unloading planned by Vova. Completion of these plans is not evidenced; legacy Airtable purpose 'summercamp and shipping H4U'.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-reclmhgQ3jzfn9gU2; EVD-recN9cYuabcVyjTpP; EVD-recixLbfaLKkFOS01; EVD-recF6Tt5AAd4wB5E5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Consignee-on-paper vs actual-goods-owner diverge by design</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADDITION / QUALIFICATION — planned handling; completion unevidenced</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recOiUWgo6VxgCpGs; ROB-recizQEts3O2pYoJn</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Loose bedding receipt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James (#logistics 24 Mar): recipients happy with pillows and blankets; plastic packaging damaged in transit; unloading media existed without shared storage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recxvO3KFoot8GwOE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Second-hand; presumed to concern the 10 Mar truck by date</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADDITION (reported)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recl6gIk4jwSbqm6p</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sep</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Warehouse stock after the period</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Not in either workbook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees's 25 observations of 2 Sep 2026 (production base): incl. ~260 fire extinguishers, 3 pallets winter clothing, ~2 pallets medical nutrition; approximate, no weights</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recdQv493Ry8o5y3d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">End-of-period context</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">ADDITION</x:t>
         </x:is>
       </x:c>
-      <x:c r="H30" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recXJEqaQUWu2GHBi</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="70" customWidth="1"/>
-    <x:col min="2" max="2" width="40" customWidth="1"/>
-    <x:col min="3" max="3" width="40" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">source_or_source_group</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="str">
-        <x:v>status / snapshot scope</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">note</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="36" hidden="0" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kees upload — Jan/Mar/May/Jun/Jul/Aug key documents, mission notes, James's workbook</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">processed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="2" t="str">
-        <x:v>Original snapshot: 37 indexed evidence records. Evidence also lists 16 additional run records, explicitly marked as awaiting incorporation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="48" hidden="0" customHeight="1">
-      <x:c r="A3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kees upload — CMR PDFs/xls (Jan, Mar, May, Jul, Aug); working May sheets; June per-consignee manifests and detail xlsx; July Airtable box-level extract; Aug detailed contents, photos (17), README.txt, 80 MB zip; WE estimate; Medical equipment sent</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>outside original snapshot; partly indexed since</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="str">
-        <x:v>Run now includes June detail, July box extract and August contents/README evidence. Reconcile those existing entries before claiming them unread or requesting them again; other listed material still requires source review.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kees's reconstruction workbook (9 tabs)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">processed (chat-attached copy)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Native Sheet revisions not inspected</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">James's reporting workbook (uploaded copy 15 Sep)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">processed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Native Sheet + XLSX copy + 2025 workbook not compared; revision lineage open</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
-      <x:c r="A6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Anja's non-private Slack export</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v>not supplied at original snapshot</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>Availability not rechecked in this PR repair. Check the shared Evidence folder before asking again.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="36" hidden="0" customHeight="1">
-      <x:c r="A7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Live Slack — targeted searches (Lithuania, mattresses, truck Jan–Feb, mission 37); DM lead-ins</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">processed (search-bounded)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>Additional shipment-message evidence is indexed outside the 37-source snapshot. Full histories remain unassessed; preserve each record’s search/identifier limits.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="48" hidden="0" customHeight="1">
-      <x:c r="A8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slack huddles — 16 Sep Anja–Kees (F0C2F1HL7L1/F0C2B53A99U)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="str">
-        <x:v>AI note indexed; transcript not processed</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="str">
-        <x:v>EVD-recJTH9lXBSM03K14 contains the AI note and records the transcript access limitation. MTG-recyjk7pw22V74PCg and the run coverage checkpoint still require reconciliation.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slack huddles — 15 Sep James–Kees</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">discovered, not processed</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MTG-recy7M3QAvanje7MP</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Slack huddles — 10 huddles registered in RUN-rechGOzgthgfAGzZu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">not re-assessed for goods content</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Cross-link pending</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Gmail kees@ — 3 threads (Van der Donk paperwork; June invoice; CMR stamping)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">snippet-level</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bodies/attachments not opened</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">WhatsApp exports (Bas, James, warehouse, drivers, donors, partners)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">not supplied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kees-held</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shipment sheets for James Truck 1 / 3 / 4 (Lithuania)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">not supplied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">James-held</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mission 33 loading list; March H4U tab; original Claude chats</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">not supplied</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Kees-held</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="36" hidden="0" customHeight="1">
-      <x:c r="A15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Airtable legacy 3 | ACTIVE LOGISTICS (appK7t991PYJ2u0DO) SHI records</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="2" t="str">
-        <x:v>source records indexed; not incorporated</x:v>
-      </x:c>
-      <x:c r="C15" s="2" t="str">
-        <x:v>Evidence for legacy SHI-0001/0002 is linked to the run. Inspect and reconcile it; this repair made no legacy-base changes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="24" hidden="0" customHeight="1">
-      <x:c r="A16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Airtable production DCA Warehouse &amp; Logistics (appivZyJTh5tQv1On) — goods still in warehouse</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="2" t="str">
-        <x:v>inventory evidence indexed; not incorporated</x:v>
-      </x:c>
-      <x:c r="C16" s="2" t="str">
-        <x:v>EVD-recdQv493Ry8o5y3d describes the 2 Sep warehouse observations. This repair made no production changes.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Asana</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">not searched</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">—</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" hidden="0" customHeight="1">
-      <x:c r="A18" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GitHub method files (dca-ai, dca-architecture)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" s="2" t="str">
-        <x:v>Claude: repo ZIPs/project knowledge; revisions unverified</x:v>
-      </x:c>
-      <x:c r="C18" s="2" t="str">
-        <x:v>PR repair checked dca-ai at df16b9c64362508aad001b7c6627290d5d095200. This does not establish which revisions Claude’s supplied ZIPs contained.</x:v>
+      <x:c r="H34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rece5DMBqpS6H0YZJ</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="36" hidden="0" customHeight="1">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">May</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Corrected May figures (G-30)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James tab 11,117 kg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Owner-scoped documents: truck 10,210 (HW 8,700 + NR 1,510) + van mission 36 527 (owner-confirmed) = 10,737 kg; category detail in the object; derived totals are run arithmetic on owner-confirmed inputs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Def. Truck May; Kees note M36; EVD-rectVzwompdkoWvb5; EVD-recsbIRbOrDpPwwWa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Replaces James's May only within the reconstruction</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="2" t="str">
+        <x:v>DERIVED TOTALS — unreviewed; confirmed inputs preserved</x:v>
+      </x:c>
+      <x:c r="H35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recH2pas3XuMv2XVy</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Jul/Aug</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reporting cadence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James's Jul/Aug tabs zero</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Owner comment: the workbook is the half-yearly Jan–Jun report; July and August belong to the year-end report; continuous insight is wanted (requirement, not finding)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa; James workbook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Absences are by design, not omissions</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RESOLVED — owner_validated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recctSkY9s9OWX9N2</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="36" hidden="0" customHeight="1">
+      <x:c r="A37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Jan/Feb</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mission 33 pallet 18 vs March P26</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Working sheet: P18 'in the van for mission 33'</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="2" t="str">
+        <x:v>March HW P26 has the same declared 315 kg, 24 boxes and medical-supplies category as January P18. This supports a candidate match, not physical identity; the Mission 33 annotation may describe an unexecuted intention.</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Truck January xlsx; Truck March (def.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="2" t="str">
+        <x:v>Physical identity, timing and whether repacking or a distinct similar pallet explains the match remain unestablished.</x:v>
+      </x:c>
+      <x:c r="G37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NEW TENSION — James/Kees to resolve (Q-B)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recqfCoNgY3BgXINx; ROB-recQHyIOyozXotKBh</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Apr</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ambulances context</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James tab: 'two ambulances delivery' (no figures)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">#marketing Mar: ~5 ambulances repaired with DCA participation; departures planned end of March; one for Bogdan's team; €2,000+€500 each per Bas (stated as a question). No delivery confirmation found.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recoHTWw0w5oqPDCT; James workbook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Question narrowed: which delivered in 6–17 Apr; vehicles as goods?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CONTEXT ADDED — delivery unresolved (Q-H)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recR0aCTKpJQY7a1T</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Dec 2025</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Armoured van receipt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James workbook: 'Mission 33 armoured van delivery' (January)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Lieke 23 Jan: Bohdan received the armoured van among DECEMBER 2025 achievements; James 3 Feb: a second vehicle not yet ready</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recT9nVfjN2snhuCi; EVD-recNRAElLXonh6n4A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James's January label a period error or a different event</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RE-READ CORRECTION — unresolved (Q-B)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-reckOFPCVHjlD6KJF</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9272,231 +10254,271 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="6" customWidth="1"/>
-    <x:col min="2" max="2" width="14" customWidth="1"/>
-    <x:col min="3" max="3" width="100" customWidth="1"/>
-    <x:col min="4" max="4" width="40" customWidth="1"/>
+    <x:col min="1" max="1" width="64" customWidth="1"/>
+    <x:col min="2" max="2" width="44" customWidth="1"/>
+    <x:col min="3" max="3" width="52" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" hidden="0" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>GATED — candidate topics only. First reconcile existing run evidence and relevant unread sources, assess sufficiency for each candidate, and run the validation-request preflight (§5) against prior answers, validations and active threads. Process relevant huddle transcripts, or record the specific access gap without treating AI notes as a transcript. Ask only the remaining operational delta. No requests are sent by this file.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">who_knows</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">question (only after evidence)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">objects</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+    <x:row r="1" ht="15" customHeight="1">
+      <x:c r="A1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_or_source_group</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">status / snapshot scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">note</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees upload — Jan/Mar/May/Jun/Jul/Aug key documents, mission notes, James's workbook</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>processed in the original source set; incomplete attachment coverage</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Evidence tab</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="48" customHeight="1">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q1</x:t>
+          <x:t xml:space="preserve">June detailed manifest; SHI-0002 LU extraction; July box-level extract; SHI-0003 README + detailed contents</x:t>
         </x:is>
       </x:c>
       <x:c r="B3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">James</x:t>
+          <x:t xml:space="preserve">processed (additional evidence, incorporated 17 Sep)</x:t>
         </x:is>
       </x:c>
       <x:c r="C3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Trucks 1 (9 Jan), 3 (28 Jan), 4 (11 Feb): how many trucks, from where (Lithuania?), what goods, what weights? Your tabs carry 32,000 + 16,000 kg 'Medical'. Kees believes mattresses. Please supply the shipment sheets/CMRs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-rec3LncyByihvWJ7w; ROB-recO2rSGDV2NHLlFu</x:t>
+          <x:t xml:space="preserve">EVD-recN9cYuabcVyjTpP; recF6Tt5AAd4wB5E5; recqqvvob4zYQpR8V; recil3LS2XJuZl9kZ; recUadXZjYAGon1Bt</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q2</x:t>
+          <x:t xml:space="preserve">Legacy Airtable appK7t991PYJ2u0DO — Shipments SHI-0001/SHI-0002</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">James / Kees</x:t>
+          <x:t xml:space="preserve">read on explicit grant (read-only); incorporated</x:t>
         </x:is>
       </x:c>
       <x:c r="C4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mission 33 (armoured van): date, what was loaded (the January sheet puts 24 boxes of medical supplies in it; Kees recalls mostly clothing), and was this the van Lieke said Bohdan received by 23 Jan or a second van?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recqfCoNgY3BgXINx; ROB-reckOFPCVHjlD6KJF</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-rec7gntN5pp4IKN6R; recixLbfaLKkFOS01; SHI-0003 absent from base</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q3</x:t>
+          <x:t xml:space="preserve">Production Airtable appivZyJTh5tQv1On — Warehouse_Inventory_Observations 2 Sep</x:t>
         </x:is>
       </x:c>
       <x:c r="B5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">James</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="2" t="str">
-        <x:v>How was June’s Donetsk food total of 3,023 kg calculated? One candidate explanation combines 2,735 kg of food with all 288 kg of SU-0011. Does the source calculation support this, and does any 148 kg also occur in house goods 193?</x:v>
-      </x:c>
-      <x:c r="D5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recefuxSdBFM8PkuY</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">read-only; incorporated as end-of-period context</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recdQv493Ry8o5y3d → G-29; no writes</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q4</x:t>
+          <x:t xml:space="preserve">Slack #logistics operational messages Mar/May/Jul/Aug; James DM 23 Jun; group DM 6 Jul</x:t>
         </x:is>
       </x:c>
       <x:c r="B6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">James</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>How were May’s categories calculated, particularly Kharkiv medical 1,510, Donetsk hygiene 572 and HW incontinence 503 kg? Check whether the proposed duplication/omission reading matches the calculation.</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recFkYkFT1rMJPJ6n</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">processed (targeted, incorporated)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">message ts values not captured (search-tool limitation)</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q5</x:t>
+          <x:t xml:space="preserve">Anja–Kees huddle 16 Sep — AI note F0C2F1HL7L1</x:t>
         </x:is>
       </x:c>
       <x:c r="B7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>After checking the planning files and existing answers: can the candidate note-to-pallet links for March P15/P32 be established? Which of P7/8/11/19 were H4U, and can note #43 be placed?</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recB37f26Q14iwW6a; ROB-rec0W2XImFq9vN3CP</x:t>
+          <x:t xml:space="preserve">processed as evidence (EVD-recJTH9lXBSM03K14)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AI note ≠ transcript; summarised wording</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q6</x:t>
+          <x:t xml:space="preserve">Anja–Kees huddle 16 Sep — transcript F0C2B53A99U</x:t>
         </x:is>
       </x:c>
       <x:c r="B8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees</x:t>
+          <x:t xml:space="preserve">UNREADABLE via connector (verified 17 Sep; unsupported type)</x:t>
         </x:is>
       </x:c>
       <x:c r="C8" s="2" t="str">
-        <x:v>After checking Kees Correction #12 and other existing answers: what evidence establishes whether January P12, P22 and P10 later shipped as the candidate March/May pallets? Record repacking or changes where known.</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh</x:t>
-        </x:is>
+        <x:v>An authorised export or another readable route is needed to process the transcript; the AI note does not substitute for it.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q7</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">James</x:t>
-        </x:is>
+          <x:t xml:space="preserve">James–Kees huddle 15 Sep</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>no artefact located in Claude’s inspected DM segment</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
-        <x:v>After reconciling the already-staged August loading/departure reports and July/August documents: what remains unresolved about inclusion in James’s workbook or the SHI-0003 departure? Do not re-ask a fact already established.</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recctSkY9s9OWX9N2; ROB-recIOT2vNEsqCjJFp</x:t>
-        </x:is>
+        <x:v>Other locations/routes were not established absent. Check accessible artefact routes before asking participants to reconstruct the huddle.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q8</x:t>
+          <x:t xml:space="preserve">Ten huddles registered under RUN-rechGOzgthgfAGzZu</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">James</x:t>
+          <x:t xml:space="preserve">not re-assessed for goods content</x:t>
         </x:is>
       </x:c>
       <x:c r="C10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mission 35 'two ambulances delivery': were ambulances delivered on 6–17 Apr, and are they to be counted as goods?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recR0aCTKpJQY7a1T</x:t>
+          <x:t xml:space="preserve">cross-link pending</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Q9</x:t>
+          <x:t xml:space="preserve">Kees's reconstruction workbook (9 tabs); James's workbook (uploaded copy 15 Sep)</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Kees / James</x:t>
+          <x:t xml:space="preserve">processed</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sender address changed from Meidoornweg to Lutmanstraat between May and June: registered-address change, template, or warehouse move?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROB-recXJEqaQUWu2GHBi</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
+          <x:t xml:space="preserve">native Sheet revisions / 2025 workbook not compared</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Gmail kees@ — 3 threads (paperwork, invoice, CMR stamping)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">snippet-level</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bodies/attachments unopened</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CMR PDFs (Jan, Mar, May, Jul, Aug); May working xlsx ×2 + NR CMR xls; June per-consignee PDFs + 'other_documents'; Aug Loading_list xlsx; 17 pallet photos; 80 MB zip; WE estimate; Medical equipment sent</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">uploaded, NOT read</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">next pass; zip not processable via Drive connector</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="36" hidden="0" customHeight="1">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">WhatsApp exports; Truck 1/3/4 sheets; Mission 33 list; March H4U tab; Anja's Slack export</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="str">
+        <x:v>not supplied/located at last recorded check</x:v>
+      </x:c>
+      <x:c r="C14" s="2" t="str">
+        <x:v>Original holders/locations remain the next source routes. March H4U attribution is already settled by Kees; export availability was not freshly checked in this repair.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="36" hidden="0" customHeight="1">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delivery/receipt documents for all shipments</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">none processed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="2" t="str">
+        <x:v>March bedding, May and August have second-hand reports. June/July cited unloading messages are plans; completion remains unestablished. No receipt processed does not mean none exists.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Asana</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">not searched</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -9505,1127 +10527,151 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" customWidth="1"/>
-    <x:col min="2" max="2" width="95" customWidth="1"/>
-    <x:col min="3" max="3" width="54" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="80" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="36" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7" customWidth="1"/>
+    <x:col min="2" max="2" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="100" customWidth="1"/>
+    <x:col min="4" max="4" width="42" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>evidence_id</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="str">
-        <x:v>display_name</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>airtable_evidence_url</x:v>
-      </x:c>
-      <x:c r="D1" s="10" t="str">
-        <x:v>original_source_url</x:v>
-      </x:c>
-      <x:c r="E1" s="10" t="str">
-        <x:v>source_reference / access limit</x:v>
-      </x:c>
-      <x:c r="F1" s="10" t="str">
-        <x:v>snapshot_scope</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="36" hidden="0" customHeight="1">
-      <x:c r="A2" s="2" t="str">
-        <x:v>EVD-recP2w8kARM0FjW3e</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="str">
-        <x:v>Drive — Goods reconstruction folder README (Kees, 16 Sep 2026) — folder structure and source roles</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recP2w8kARM0FjW3e</x:v>
-      </x:c>
-      <x:c r="D2" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E2" s="12" t="str">
-        <x:v>Drive file 1ZdoOgAA8GJXn_3MNPzKAFceea1pu_1l9; modified 2026-09-16T20:44:43Z. Folder created 2026-09-16T21:51Z with subfolders Truck info (01 Jan, 02 Mar, 03 May, 04 Jun, 05 Jul, 06 Aug), Missions (van) (33, 34, 35, 36, 38, 39), Earlier valuations.</x:v>
-      </x:c>
-      <x:c r="F2" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="24" hidden="0" customHeight="1">
-      <x:c r="A3" s="2" t="str">
-        <x:v>EVD-reck3RM4FAhiKan1j</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>Drive — DCA-Goods-Reconstruction-Notes-for-Kees.md (Anja, 16 Sep 2026) — source-supply instructions and boundaries</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reck3RM4FAhiKan1j</x:v>
-      </x:c>
-      <x:c r="D3" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="str">
-        <x:v>Drive file 1KVawWMA2Qk4ebcYfZ89AFkfpJz_oxxm5; modified 2026-09-16T21:03:59Z</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="60" hidden="0" customHeight="1">
-      <x:c r="A4" s="2" t="str">
-        <x:v>EVD-recOfWtk5eGnuCqd2</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>Google Sheet — DCA_goods_reconstruction_2026_Jan-Jun (Kees + prior Claude chat) — 9 tabs, read as chat attachment</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recOfWtk5eGnuCqd2</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E4" s="12" t="str">
-        <x:v>Sheet 172U-YYZQQqc2qIebYuQeSNIHRSSdeR7H78y0F3koy-w; content read from the copy attached to this Claude chat (17 Sep 2026); tabs README, Comparison, Valuation_Status, Shipments, Goods_Lines, Rates, Open_Items, Corrections, Detail_Gaps
-Limit: Read from chat-attached copy; native sheet not opened in this run; the originating Claude chat is not readable (only the workbook survives).</x:v>
-      </x:c>
-      <x:c r="F4" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="60" hidden="0" customHeight="1">
-      <x:c r="A5" s="2" t="str">
-        <x:v>EVD-reci8DsW1gdgoWPg6</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="str">
-        <x:v>Drive — DCA goods delivered for 2026.xlsx (uploaded copy, mod 15 Sep 2026) — James's monthly kg/€ reporting, Sep 2025–Aug 2026, Jan–Jun total 98,162 kg / €782,199</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reci8DsW1gdgoWPg6</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1OC5vrenD58ewHgy7cKCbKrFRDvygpcNR/view</x:v>
-      </x:c>
-      <x:c r="E5" s="12" t="str">
-        <x:v>Drive file 1OC5vrenD58ewHgy7cKCbKrFRDvygpcNR (copy modified 2026-09-15T15:54:41Z). Prompt names native Sheet 1h0LgqvMB_tbL4XbkoDgrGJ-o9IjwC6wmvTgwiQk0FYU and XLSX 1qqJp4rItaMq5WbIwhwR476Wit5SHZXYo — version lineage not yet established.
-Limit: Text export without cell coordinates; native Google Sheet and its revision history not yet inspected; region attribution logic is James's and is not documented in the file.</x:v>
-      </x:c>
-      <x:c r="F5" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="60" hidden="0" customHeight="1">
-      <x:c r="A6" s="2" t="str">
-        <x:v>EVD-recpYmNnGlJCfftyh</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v>Drive — Truck January 2026.xlsx — working sheet 33, HW and NR CMR sheets, Total (20 pallets / 10,036 kg)</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recpYmNnGlJCfftyh</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1ETJQCmiyKfLEQ2G_pO4xee4s1csYN-uJ/view</x:v>
-      </x:c>
-      <x:c r="E6" s="12" t="str">
-        <x:v>Drive file 1ETJQCmiyKfLEQ2G_pO4xee4s1csYN-uJ (uploaded copy, modified 2026-09-16T07:06:11Z, created in Drive 2026-09-16T21:51Z). Prompt source guide names native Sheet 1CuyHsp8J3WrI1u9dMvh2HWNEaC3-LlUlqw7Ko3WK1lc as 'Truck January 2026' — not yet compared.
-Limit: Uploaded Excel copy read through Drive text export; cell coordinates not exposed, sheet boundaries inferred; original Google Sheet and revision history not inspected; CMR PDFs (separate files) not yet compared.</x:v>
-      </x:c>
-      <x:c r="F6" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
+    <x:row r="1" ht="24" hidden="0" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>UNSENT DRAFT TOPICS — 2026-09-17T19:42:35.495Z. Q-E/G/I/J and August departure are answered; Q-F’s no-repacking assessment is preserved; Q-D remains dropped. Claude recorded an earlier preflight. Check relevant unread evidence and current answers/active threads before releasing these five residual topics. This consistency repair did not conduct a new cross-platform preflight or send requests.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">who_knows</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">remaining operational question (neutral; unsent)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">objects</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Q-A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">For January–February 2026 your workbook lists Truck 1 (9 Jan), Truck 3 (28 Jan) and Truck 4 (11 Feb) with 48,000 kg 'Medical' in total. Kees holds no documents for these. Could you share whatever documents exist and describe what these trucks carried, from where, and how the weights were determined?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-rec3LncyByihvWJ7w; ROB-recO2rSGDV2NHLlFu</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Q-B</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James + Kees</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mission 33: Lieke's message places Bohdan's armoured-van receipt in December 2025, while your workbook lists 'Mission 33 armoured van delivery' under January — what does the January entry refer to, when did mission 33 run, and what was loaded? (The January sheet put pallet 18 — 24 medical boxes, 315 kg — in the van, but an identical pallet appears on the March truck.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recqfCoNgY3BgXINx; ROB-reckOFPCVHjlD6KJF</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Q-C</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">June reporting: could you explain how the June figures were calculated (Donetsk food 3,023; house goods 193; total 7,718 vs manifest 7,570.5), and check whether the 148 kg monitors ended up counted twice?</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recefuxSdBFM8PkuY</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Q-F</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Kees</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="str">
+        <x:v>Carry-over candidates: P12→Mar NR P1; P16→Mar NR P2; P18→Mar HW P26; P22→Mar P27 OR P28; P10→May HW P11. Your 99% no-repacking assessment is recorded. Which individual identities can you confirm from knowledge or records, and what happened to unmatched P4/P6/P8/P26? Similarity alone is not a confirmed identity.</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
-      <x:c r="A7" s="2" t="str">
-        <x:v>EVD-reci7q8O3ccosy82w</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Truck January: Working sheet not final; Total sheet + CMR leading</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reci7q8O3ccosy82w</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E7" s="12" t="str">
-        <x:v>Drive file 1mceuLiWgz1ksglaWF1Ha_gAWPBhfqQpl; modified 2026-09-16T20:32:50Z</x:v>
-      </x:c>
-      <x:c r="F7" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="24" hidden="0" customHeight="1">
-      <x:c r="A8" s="2" t="str">
-        <x:v>EVD-recdaLZzXrb5e9Nu1</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Missing information: two January trucks from Lithuania (mattresses)</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdaLZzXrb5e9Nu1</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E8" s="12" t="str">
-        <x:v>Drive file 1uJ8cnQ6yZVwAJ-siXR05AWSDABZCujbU; modified 2026-09-16T20:30:18Z</x:v>
-      </x:c>
-      <x:c r="F8" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="84" hidden="0" customHeight="1">
-      <x:c r="A9" s="2" t="str">
-        <x:v>EVD-recuxxn3mlOO1aDUI</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="str">
-        <x:v>Drive — Truck March (def.) (1).xlsx — NR (7 pallets / 4,226 kg) and HW (24 pallets / 15,093 kg) CMR sheets, 10 Mar 2026</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recuxxn3mlOO1aDUI</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1DoitCvlni5TBXjRbZi5cJqxjEDv0X3oW/view</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="str">
-        <x:v>Drive file 1DoitCvlni5TBXjRbZi5cJqxjEDv0X3oW; file modified 2026-03-10T06:57:18Z. Prompt source guide names Drive copy 1B22T52KP5sWZccCTyiu9tzmi6QV-aPBW (not yet compared). Companion CMR xls in same folder: CMR Nezlamna Rodyna.xls (15F3lL001NPwMnH6TB_RzX_f_t60TS5l-, mod 2026-03-10T06:57Z), CMR Help Window.xls (1IdM0Teek8pKOFlP48hG3WZ8KcqIzAAsd, mod 2026-03-18T05:41Z) — not yet read.
-Limit: Uploaded Excel read via text export (no cell coordinates); no H4U tab present although Kees's reconstruction cites an 'H4U tab' for pallets 7, 8, 11, 15, 19, 32 — that source is not in the supplied file. Companion CMR .xls files not yet read.</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" hidden="0" customHeight="1">
-      <x:c r="A10" s="2" t="str">
-        <x:v>EVD-recXV9ispSK3XyfXd</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — WhatsApp screenshots: pallet numbers do not match CMR; match by content or leave unresolved</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recXV9ispSK3XyfXd</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E10" s="12" t="str">
-        <x:v>Drive file 1cP1gg5-d6DEjaaKqEHOJLgOrzlHbg_5U; modified 2026-09-16T20:39:54Z</x:v>
-      </x:c>
-      <x:c r="F10" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="36" hidden="0" customHeight="1">
-      <x:c r="A11" s="2" t="str">
-        <x:v>EVD-recCEC5J1MVeGwWQb</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="str">
-        <x:v>WhatsApp screenshot 1/3 — Kees pallet notes #32–#39 (Feb 2026 packing for March truck)</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recCEC5J1MVeGwWQb</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E11" s="12" t="str">
-        <x:v>Drive file 1rdJo4Iv5NFOcMjS-aOpEBZIkmAPV1N-T (945×2048 px); screenshot taken 2026-09-16 11:17 (device clock); WhatsApp search box shows 'Februa'; result counter '1 van 5 resultaten'
-Limit: Screenshot only: no dates, no chat name, no recipient, partial last message; original chat export not supplied.</x:v>
-      </x:c>
-      <x:c r="F11" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="24" hidden="0" customHeight="1">
-      <x:c r="A12" s="2" t="str">
-        <x:v>EVD-recdkvcEAnpQD59Sm</x:v>
-      </x:c>
-      <x:c r="B12" s="2" t="str">
-        <x:v>WhatsApp screenshot 2/3 — Kees pallet notes #38–#43 incl. H4U pallets (Feb 2026)</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdkvcEAnpQD59Sm</x:v>
-      </x:c>
-      <x:c r="D12" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E12" s="12" t="str">
-        <x:v>Drive file 1n7lyb989GVI_VhiGw1QcKMuzvZnt776z; screenshot 2026-09-16 11:18; search 'Februa'
-Limit: Screenshot only; no dates; overlaps screenshot 3 for 15:43–17:07 messages.</x:v>
-      </x:c>
-      <x:c r="F12" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="24" hidden="0" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>EVD-recd4zaJNUefVVHrt</x:v>
-      </x:c>
-      <x:c r="B13" s="2" t="str">
-        <x:v>WhatsApp screenshot 3/3 — Kees pallet notes #44–#46 (Feb 2026)</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recd4zaJNUefVVHrt</x:v>
-      </x:c>
-      <x:c r="D13" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E13" s="12" t="str">
-        <x:v>Drive file 1QbNhcb7fmrPRO7cr_qVp9CM2VmUFXdaB; screenshot 2026-09-16 11:18; search 'Februa'
-Limit: Screenshot only; at least one message after #46 not captured.</x:v>
-      </x:c>
-      <x:c r="F13" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="96" hidden="0" customHeight="1">
-      <x:c r="A14" s="2" t="str">
-        <x:v>EVD-recDe227kjiqwpZc5</x:v>
-      </x:c>
-      <x:c r="B14" s="2" t="str">
-        <x:v>Drive — Def. Truck May 6 2026.xlsx (uploaded copy) — HW 16 pallets / 8,700 kg incl. H4U Ludmila/Zhytomir pallets 1–4; NR 4 pallets / 1,510 kg; total 806 boxes / 10,210 kg</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recDe227kjiqwpZc5</x:v>
-      </x:c>
-      <x:c r="D14" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E14" s="12" t="str">
-        <x:v>Drive file 1TVO8UH7ynwxAIP-qKU9I9Ll00DumkmC1 (uploaded copy modified 2026-09-16T14:55:04Z). Same underlying workbook as prompt-named native Sheet 1wMyxL1e_KNzUj1N__pmcC2lHHd1mIjF1_RReIHB8viQ and as prior-run Evidence EVD-recf68zLDBfKnZf0A / EVD-rec340ub5uaSKcVJE (RUN-rechGOzgthgfAGzZu) — not independent corroboration. Companions in folder: Truck May .xlsx (1Bk2CLJaI1ZAq7lzKPPCeqYEcX1cyiBym), Truck May 6 2026 (1).xlsx (1-5Qy59-YD01_FWvaNBT_T87xXiUm3yH-, mod 2026-05-06T01:50Z), CMR Nezlamna Rodyna May 2026.xls (11gbNZ7OjOoUnZNYYpWMk-2vtAdvb_MC2) — not yet read.
-Limit: Text export flattens sheets; cell references reconstructed from row order. Truck May .xlsx working version and CMR xls not yet compared.</x:v>
-      </x:c>
-      <x:c r="F14" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="60" hidden="0" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>EVD-recjovJhHNHrkGZb3</x:v>
-      </x:c>
-      <x:c r="B15" s="2" t="str">
-        <x:v>Drive — Manifest_SHI-0002_Total kopie.pdf — June truck 24 Jun 2026, Zhytomyr/Makariv, 437 boxes / 7,570.5 kg (HW 3,745.5; Salim 3,632; Lifeline 193)</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recjovJhHNHrkGZb3</x:v>
-      </x:c>
-      <x:c r="D15" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E15" s="12" t="str">
-        <x:v>Drive file 1d0t1DS4q3HbHXmb0r2FvYsNNLvMHQuuq (file modified 2026-06-24T08:44:15Z). Copies of the same manifest set exist in the operational June Documents folder (1ljdisl-eBtNJvDlWflx2bgoQH0QItdkY) and the Manifest 2026 bundle — not independent sources. Companions: Manifest_SHI-0002_HW/Salim/Lifeline kopie.pdf, 1. Detailed_Manifest_SHI-0002 kopie.xlsx (1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM), SHI-0002_pallet_detail_extraction.xlsx — not yet read.</x:v>
-      </x:c>
-      <x:c r="F15" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="36" hidden="0" customHeight="1">
-      <x:c r="A16" s="2" t="str">
-        <x:v>EVD-recsWgu6FH9FSh1AU</x:v>
-      </x:c>
-      <x:c r="B16" s="2" t="str">
-        <x:v>Drive — SHI-0002 Pallet Detail Extraction README (derived Claude output, Kees's chat) — no pallet photos exist; Monitors vs TVs on SU-0011 unresolved</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recsWgu6FH9FSh1AU</x:v>
-      </x:c>
-      <x:c r="D16" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E16" s="12" t="str">
-        <x:v>Drive file 1nyEZIRg9_1aS3DK9_pf6W6jfPhL2Ngyz (modified 2026-09-16T18:07:10Z). Derived from a Claude chat about SHI-0002 ('Shipment 0002 pallet organization'); the underlying chat is not accessible to this run.
-Limit: AI-generated summary of an inaccessible chat; the companion xlsx and 'other_documents' folder not yet read.</x:v>
-      </x:c>
-      <x:c r="F16" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" hidden="0" customHeight="1">
-      <x:c r="A17" s="2" t="str">
-        <x:v>EVD-rec3AuCzNvlH0aA5H</x:v>
-      </x:c>
-      <x:c r="B17" s="2" t="str">
-        <x:v>Drive — Manifest_SHI-0001..pdf (driver &amp; customs manifest) — July truck dispatch 4 Jul 2026, Kharkiv, 32 pallets / 1,008 boxes / 15,260 kg + 51 bags bedding 510 kg loose</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec3AuCzNvlH0aA5H</x:v>
-      </x:c>
-      <x:c r="D17" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E17" s="12" t="str">
-        <x:v>Drive file 1w1A4r0GgTIeLfYNt5EaBPPOSMshgQ-wH (modified 2026-09-16T17:22:37Z). Prompt names operational copy '5. July Manifest_SHI-0001..pdf' 1Y7cDxT_pEvPKmoQF1Ac0OnKV3I-nYnLL — same document, not independent. CMR PDFs in folder: CMR_SHI-0001_HW kopie.pdf (1ijQJZlohLI3aLLgr19OayewgfHHBIFCJ), CMR_SHI-0001_NR kopie.pdf (1pwtjruY-5V3E34zvcUKhUc4aXlfkS6e8), both modified 2026-06-27 — not yet read.</x:v>
-      </x:c>
-      <x:c r="F17" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="24" hidden="0" customHeight="1">
-      <x:c r="A18" s="2" t="str">
-        <x:v>EVD-reccKtLmFYdcbgiig</x:v>
-      </x:c>
-      <x:c r="B18" s="2" t="str">
-        <x:v>Drive — Manifest_SHI-0001_detail.pdf (internal detailed manifest) — July truck subcategory detail per pallet, HW 19 / NR 13 pallets</x:v>
-      </x:c>
-      <x:c r="C18" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reccKtLmFYdcbgiig</x:v>
-      </x:c>
-      <x:c r="D18" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E18" s="12" t="str">
-        <x:v>Drive file 1t3ygcUmwXe9sXtFtnovOx5ATrp6Tt-EX (file modified 2026-06-26T19:30:26Z). Companion Airtable extract: SHI-0001_box_level_extract (source Airtable).xlsx (1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq) — not yet read.</x:v>
-      </x:c>
-      <x:c r="F18" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="84" hidden="0" customHeight="1">
-      <x:c r="A19" s="2" t="str">
-        <x:v>EVD-rec0F392MGFzyMkvY</x:v>
-      </x:c>
-      <x:c r="B19" s="2" t="str">
-        <x:v>Drive — Loading_list_SHI-0003.pdf — August truck, list dated 20 Aug 2026, Kharkiv: HW 15 pallets / 649 boxes / 8,779 kg; NR 5 pallets / 164 boxes / 1,511 kg</x:v>
-      </x:c>
-      <x:c r="C19" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec0F392MGFzyMkvY</x:v>
-      </x:c>
-      <x:c r="D19" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E19" s="12" t="str">
-        <x:v>Drive file 1W8-8AgC55oirp0T4B97S5gGrWbeT5k4q (modified 2026-09-16T19:58:03Z). Companions: Loading_list_SHI-0003.xlsx (1pLz1ERu47AFPmxA5YioIx3kFXLkn1mGK), SHI-0003_detailed_contents.xlsx (1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky), CMR_SHI-0003_HW.pdf (1Mjxce9QNTf9T1B2eqm-od6wWwqCpCpXg), CMR_SHI-0003_NR.pdf (1uZwO3DwNOdqMJOwlmT_KYNCZJodG0Lr6), 17 pallet photos in '02 Source photos' (1FipL_kKif52APTZBFIO8_hYvmyAIgLSG), 'Source data SHI-0003_package.zip' 80 MB (1mDd0-el_ID7zjmUbazsDvYSYBRxOjSRf) — companions not yet read; zip not processable through the Drive connector.</x:v>
-      </x:c>
-      <x:c r="F19" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="24" hidden="0" customHeight="1">
-      <x:c r="A20" s="2" t="str">
-        <x:v>EVD-reczExBGAKskkWAOy</x:v>
-      </x:c>
-      <x:c r="B20" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Mission 33 armoured van: no loading list; from memory mostly second-hand clothing (~700 kg per James)</x:v>
-      </x:c>
-      <x:c r="C20" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reczExBGAKskkWAOy</x:v>
-      </x:c>
-      <x:c r="D20" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E20" s="12" t="str">
-        <x:v>Drive file 1xye4e8GiGtAIZsSNiSxupfVuBBVZX0US; modified 2026-09-16T21:39:25Z</x:v>
-      </x:c>
-      <x:c r="F20" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="24" hidden="0" customHeight="1">
-      <x:c r="A21" s="2" t="str">
-        <x:v>EVD-recQPFCLknLS7NRoI</x:v>
-      </x:c>
-      <x:c r="B21" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Mission 34 (Feb): 13 Nutridrink boxes 260 kg confirmed; earlier price statements</x:v>
-      </x:c>
-      <x:c r="C21" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recQPFCLknLS7NRoI</x:v>
-      </x:c>
-      <x:c r="D21" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E21" s="12" t="str">
-        <x:v>Drive file 1ARFYAIZzkDqhrFdOgJRr2tHYvFQgiUzG; modified 2026-09-16T21:50:43Z
-Limit: No original loading list for Mission 34 supplied; note is a recollection.</x:v>
-      </x:c>
-      <x:c r="F21" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="24" hidden="0" customHeight="1">
-      <x:c r="A22" s="2" t="str">
-        <x:v>EVD-recDpcZyE0q3nqz4p</x:v>
-      </x:c>
-      <x:c r="B22" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Mission 35 (6 Apr) loading list as given: 6 lines, 686 kg, mostly Lighthouse Makariv</x:v>
-      </x:c>
-      <x:c r="C22" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recDpcZyE0q3nqz4p</x:v>
-      </x:c>
-      <x:c r="D22" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E22" s="12" t="str">
-        <x:v>Drive file 1maR4s1f-b6_YzrsxZtA9xUy_obomXtGa; modified 2026-09-16T21:39:54Z
-Limit: Original loading list document not supplied; transcription by Kees.</x:v>
-      </x:c>
-      <x:c r="F22" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="24" hidden="0" customHeight="1">
-      <x:c r="A23" s="2" t="str">
-        <x:v>EVD-recRp4HzSsJj4FwZ5</x:v>
-      </x:c>
-      <x:c r="B23" s="2" t="str">
-        <x:v>Kees note — Mission 36: 507 kg stated; 527 kg line sum; conflict unresolved</x:v>
-      </x:c>
-      <x:c r="C23" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recRp4HzSsJj4FwZ5</x:v>
-      </x:c>
-      <x:c r="D23" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E23" s="12" t="str">
-        <x:v>Drive file 1g4CqV1AS7a8JMG6OJru3rdfck2kNadc8; modified 2026-09-16T21:41:32Z
-Limit: Original list not supplied; transcription.</x:v>
-      </x:c>
-      <x:c r="F23" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="24" hidden="0" customHeight="1">
-      <x:c r="A24" s="2" t="str">
-        <x:v>EVD-reckPmE5zeLQ5sBhj</x:v>
-      </x:c>
-      <x:c r="B24" s="2" t="str">
-        <x:v>Kees note (16 Sep 2026) — Mission 38 (11–21 Jul) loading list sent to James 10 Jul: 55 boxes medical food 510 kg + 2 boxes food 15 kg</x:v>
-      </x:c>
-      <x:c r="C24" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reckPmE5zeLQ5sBhj</x:v>
-      </x:c>
-      <x:c r="D24" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E24" s="12" t="str">
-        <x:v>Drive file 1V-YWm2JDtbz78aHWY75m8zTua3bkepZr; modified 2026-09-16T21:48:10Z
-Limit: The 10 Jul message to James not yet located in Slack/Gmail.</x:v>
-      </x:c>
-      <x:c r="F24" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="24" hidden="0" customHeight="1">
-      <x:c r="A25" s="2" t="str">
-        <x:v>EVD-recHxzwdLF80ShqFA</x:v>
-      </x:c>
-      <x:c r="B25" s="2" t="str">
-        <x:v>Drive — Mission_39_Loading_List.pdf — van loading list prepared for James, 20 Aug 2026: 8 lines, 167 units, 1,286 kg</x:v>
-      </x:c>
-      <x:c r="C25" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recHxzwdLF80ShqFA</x:v>
-      </x:c>
-      <x:c r="D25" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E25" s="12" t="str">
-        <x:v>Drive file 1pTtMGm8LcUJs4To6V0zaOxxQqqsa_FIV; modified 2026-09-16T19:42:27Z; document header 'Prepared for James | 20 August 2026'</x:v>
-      </x:c>
-      <x:c r="F25" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="24" hidden="0" customHeight="1">
-      <x:c r="A26" s="2" t="str">
-        <x:v>EVD-recMeesVNstFr8kZf</x:v>
-      </x:c>
-      <x:c r="B26" s="2" t="str">
-        <x:v>Kees reference (16 Sep 2026) — Van mission prices as stated in chat (earlier evaluation, not definitive)</x:v>
-      </x:c>
-      <x:c r="C26" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recMeesVNstFr8kZf</x:v>
-      </x:c>
-      <x:c r="D26" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E26" s="12" t="str">
-        <x:v>Drive file 1bBKpvHTygpB1X3lyyQ23GnlqbhBDIVcb; modified 2026-09-16T21:50:43Z</x:v>
-      </x:c>
-      <x:c r="F26" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="24" hidden="0" customHeight="1">
-      <x:c r="A27" s="2" t="str">
-        <x:v>EVD-recT9nVfjN2snhuCi</x:v>
-      </x:c>
-      <x:c r="B27" s="2" t="str">
-        <x:v>Slack #marketing — Lieke, 23 Jan 2026: 'in a week, Bohdan received an armored van, we've sent three trucks … preparing our next mission, mission 33'</x:v>
-      </x:c>
-      <x:c r="C27" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recT9nVfjN2snhuCi</x:v>
-      </x:c>
-      <x:c r="D27" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E27" s="12" t="str">
-        <x:v>Slack channel C037S4YL6MT; message 2026-01-23 20:58:26 CET by lieke heil (U038N98335E); message ts not captured by the search tool (limitation).</x:v>
-      </x:c>
-      <x:c r="F27" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="24" hidden="0" customHeight="1">
-      <x:c r="A28" s="2" t="str">
-        <x:v>EVD-recVH7fncxcyqfkoh</x:v>
-      </x:c>
-      <x:c r="B28" s="2" t="str">
-        <x:v>Slack #marketing — Bas, 16 Feb 2026: truck from NL €3,500 vs truck from Lithuania €2,500 (winter/heating campaign)</x:v>
-      </x:c>
-      <x:c r="C28" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recVH7fncxcyqfkoh</x:v>
-      </x:c>
-      <x:c r="D28" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E28" s="12" t="str">
-        <x:v>Slack channel C037S4YL6MT; message 2026-02-16 14:57:24 CET by Bas (U038JKTA7QQ); ts not captured.</x:v>
-      </x:c>
-      <x:c r="F28" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="36" hidden="0" customHeight="1">
-      <x:c r="A29" s="2" t="str">
-        <x:v>EVD-reclaxOv0x7yGfjXB</x:v>
-      </x:c>
-      <x:c r="B29" s="2" t="str">
-        <x:v>Drive doc — Emergency Appeal for Ukraine (Feb 2026 campaign): 'We have already sent 5 trucks in 2026'; two winter trucks; mission 35 on 6 April</x:v>
-      </x:c>
-      <x:c r="C29" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reclaxOv0x7yGfjXB</x:v>
-      </x:c>
-      <x:c r="D29" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E29" s="12" t="str">
-        <x:v>Google Doc 1OdP715UQCwQEvIMAKGL4sazamrxzdfDVti1XEHhkdHk; read 17 Sep 2026 (current revision; historical revision at time of posting not inspected).
-Limit: Current revision read; edits after Feb 2026 possible.</x:v>
-      </x:c>
-      <x:c r="F29" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="24" hidden="0" customHeight="1">
-      <x:c r="A30" s="2" t="str">
-        <x:v>EVD-reccKKxnjMSvh7bql</x:v>
-      </x:c>
-      <x:c r="B30" s="2" t="str">
-        <x:v>Slack DM Kees–James — Kees, 4 Feb 2026: take only nutrition expiring before March in the van; rest by truck end of month</x:v>
-      </x:c>
-      <x:c r="C30" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reccKKxnjMSvh7bql</x:v>
-      </x:c>
-      <x:c r="D30" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E30" s="12" t="str">
-        <x:v>Slack DM D0AC3M2J5QE; message 2026-02-04 16:14:32 CET by Kees (U0ABU10D2KD); ts not captured.</x:v>
-      </x:c>
-      <x:c r="F30" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="24" hidden="0" customHeight="1">
-      <x:c r="A31" s="2" t="str">
-        <x:v>EVD-recNRAElLXonh6n4A</x:v>
-      </x:c>
-      <x:c r="B31" s="2" t="str">
-        <x:v>Slack #fundraising — James, 3 Feb 2026: 'Let's see how Bohdan does with the van first. I will check also when the van may be ready for sending to UA'</x:v>
-      </x:c>
-      <x:c r="C31" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recNRAElLXonh6n4A</x:v>
-      </x:c>
-      <x:c r="D31" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E31" s="12" t="str">
-        <x:v>Slack channel C037USZ92V8; message 2026-02-03 12:24:25 CET by James (U05DKS7C3U0); ts not captured.</x:v>
-      </x:c>
-      <x:c r="F31" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="24" hidden="0" customHeight="1">
-      <x:c r="A32" s="2" t="str">
-        <x:v>EVD-recLS1vD7QUXfGrLm</x:v>
-      </x:c>
-      <x:c r="B32" s="2" t="str">
-        <x:v>Slack DM Kees–James — Kees relays H4U (Johan), 14 May 2026: offer of ~200 beds/mattresses from a residential complex in Zaandam</x:v>
-      </x:c>
-      <x:c r="C32" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recLS1vD7QUXfGrLm</x:v>
-      </x:c>
-      <x:c r="D32" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E32" s="12" t="str">
-        <x:v>Slack DM D0AC3M2J5QE; message 2026-05-14 09:14:02 CEST by Kees; ts not captured.</x:v>
-      </x:c>
-      <x:c r="F32" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="24" hidden="0" customHeight="1">
-      <x:c r="A33" s="2" t="str">
-        <x:v>EVD-recJI4FH0GVHLhByd</x:v>
-      </x:c>
-      <x:c r="B33" s="2" t="str">
-        <x:v>Slack group DM Bas/James/Kees — James, 3 &amp; 6 Jul 2026: two missions at once; 'goods from last transport have not been picked up by everyone'; mission 37 = truck drivers' journey (e-toll, Polish road inspection)</x:v>
-      </x:c>
-      <x:c r="C33" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recJI4FH0GVHLhByd</x:v>
-      </x:c>
-      <x:c r="D33" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E33" s="12" t="str">
-        <x:v>Slack group DM (Bas, James, Kees); messages 2026-07-03 10:31:58 CEST and 2026-07-06 10:10:39 CEST by James (U05DKS7C3U0); ts not captured.</x:v>
-      </x:c>
-      <x:c r="F33" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="24" hidden="0" customHeight="1">
-      <x:c r="A34" s="2" t="str">
-        <x:v>EVD-recOX5n0nZClxgYdP</x:v>
-      </x:c>
-      <x:c r="B34" s="2" t="str">
-        <x:v>Slack #logistics — James &amp; Bas, 3 Jul 2026: WhatsApp group for mission 37 with the two drivers; 'they start driving at 08:00 this Saturday'</x:v>
-      </x:c>
-      <x:c r="C34" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recOX5n0nZClxgYdP</x:v>
-      </x:c>
-      <x:c r="D34" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E34" s="12" t="str">
-        <x:v>Slack channel C037X71FME0; James 2026-07-03 14:57:43 CEST; Bas reply 2026-07-03 15:07:19 CEST; ts not captured.</x:v>
-      </x:c>
-      <x:c r="F34" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="24" hidden="0" customHeight="1">
-      <x:c r="A35" s="2" t="str">
-        <x:v>EVD-recYfz6sYRCJERXPw</x:v>
-      </x:c>
-      <x:c r="B35" s="2" t="str">
-        <x:v>Slack #ukraine — DCA Bot, 13 Sep 2026: mission dates 34–39; 'Mission 37' used for the 4 July truck and for camp fundraising (derivative AI summary)</x:v>
-      </x:c>
-      <x:c r="C35" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recYfz6sYRCJERXPw</x:v>
-      </x:c>
-      <x:c r="D35" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E35" s="12" t="str">
-        <x:v>Slack #ukraine; Dutch Civilian Action Bot message 2026-09-13 20:34:59 CEST; ts not captured.
-Limit: AI summary; underlying sources not enumerated in the message.</x:v>
-      </x:c>
-      <x:c r="F35" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="60" hidden="0" customHeight="1">
-      <x:c r="A36" s="2" t="str">
-        <x:v>EVD-recZJ8yS3SefenE0j</x:v>
-      </x:c>
-      <x:c r="B36" s="2" t="str">
-        <x:v>Gmail — Kees → W.B. van der Donk Transport, 27 Jun–3 Jul 2026: paperwork for the Kharkiv transport (two CMRs + manifest), manifest adjustment 3 Jul, confirmation letter</x:v>
-      </x:c>
-      <x:c r="C36" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recZJ8yS3SefenE0j</x:v>
-      </x:c>
-      <x:c r="D36" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E36" s="12" t="str">
-        <x:v>Gmail thread 19f0888eec7ab63d; messages 19f088c95bd1c9e9 (2026-06-27T10:07Z), 19f274c40f2c9867 (2026-07-03T09:25Z), 19f27cb22105e74c (2026-07-03T11:44Z). Related thread 19f2908cb1d871a4 'DCA Humanitarian Transport Support Letter' (2026-07-03, to info@wbvanderdonktransport.nl). Bodies read at snippet level only; attachments not opened.
-Limit: Snippets only; attachments (CMRs, manifest versions) not compared with the Drive copies.</x:v>
-      </x:c>
-      <x:c r="F36" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="24" hidden="0" customHeight="1">
-      <x:c r="A37" s="2" t="str">
-        <x:v>EVD-recibLdWHNIJanw5J</x:v>
-      </x:c>
-      <x:c r="B37" s="2" t="str">
-        <x:v>Gmail — 'DCA invoice for truck June 2026' (Kees → Tomas/finance, 6 Jul–13 Aug 2026): invoice for the truck loaded 24 June; Ukraine asking whether paid (12 Aug)</x:v>
-      </x:c>
-      <x:c r="C37" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recibLdWHNIJanw5J</x:v>
-      </x:c>
-      <x:c r="D37" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E37" s="12" t="str">
-        <x:v>Gmail thread 19f3733ade8be4d1; messages 19f3734b144bd05e (2026-07-06), 19f3bdcdfd5cc1d7 (2026-07-07, Tomas), 19ff5737c9a65542 (2026-08-12), 19ff9e45fc3ecded (2026-08-13). Snippets only; invoice attachment not opened.</x:v>
-      </x:c>
-      <x:c r="F37" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="36" hidden="0" customHeight="1">
-      <x:c r="A38" s="2" t="str">
-        <x:v>EVD-recx7hibtO7QmFOev</x:v>
-      </x:c>
-      <x:c r="B38" s="2" t="str">
-        <x:v>Gmail — 'CMR papers DCA' (Kees ↔ Olena/Elena Beresovskaya, 14–18 Aug 2026): stamped CMR needed for the carrier's bank currency check; James sent the documents 17 Aug</x:v>
-      </x:c>
-      <x:c r="C38" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recx7hibtO7QmFOev</x:v>
-      </x:c>
-      <x:c r="D38" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E38" s="12" t="str">
-        <x:v>Gmail thread 19ef5524fa59492e; messages 19ffeb7611834a00 (2026-08-14), 19ffeeaf05df6620 (2026-08-14, Olena), 1a00f520cb360848 (2026-08-17), 1a0160cda53379e3 (2026-08-18, stamped documents), 1a01631a93217beb (2026-08-18, Olena). Thread has ≥5 messages; earlier messages (thread ID dates from June) not read.</x:v>
-      </x:c>
-      <x:c r="F38" s="12" t="str">
-        <x:v>Original 37-source snapshot</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="48" hidden="0" customHeight="1">
-      <x:c r="A39" s="6" t="str">
-        <x:v>EVD-recN9cYuabcVyjTpP</x:v>
-      </x:c>
-      <x:c r="B39" s="6" t="str">
-        <x:v>Drive — 1. Detailed_Manifest_SHI-0002 kopie.xlsx — June truck per-recipient detail: HW 6 pallets/236 boxes/3,745.5 kg; Salim 6/196/3,632; Lifeline 5/193; loading Noordwijkerhout 24.06.2026</x:v>
-      </x:c>
-      <x:c r="C39" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recN9cYuabcVyjTpP</x:v>
-      </x:c>
-      <x:c r="D39" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM/view</x:v>
-      </x:c>
-      <x:c r="E39" s="12" t="str">
-        <x:v>Drive file ID 1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM; file modified 2026-06-24T07:24Z; uploaded to Intake folder 2026-09-16
-Limit: Declared/planned document generated before or on loading day; not evidence of physical load or receipt. Read via Drive text export (sheet boundaries flattened).</x:v>
-      </x:c>
-      <x:c r="F39" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="36" hidden="0" customHeight="1">
-      <x:c r="A40" s="6" t="str">
-        <x:v>EVD-recF6Tt5AAd4wB5E5</x:v>
-      </x:c>
-      <x:c r="B40" s="6" t="str">
-        <x:v>Drive — SHI-0002_pallet_detail_extraction.xlsx (derived Claude output from Kees's June shipment chat) — LU-level detail, correction history, Monitors vs TVs conflict</x:v>
-      </x:c>
-      <x:c r="C40" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recF6Tt5AAd4wB5E5</x:v>
-      </x:c>
-      <x:c r="D40" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1RejG__2xMqZe9dvY65BEP1EcjkxLdY4e/view</x:v>
-      </x:c>
-      <x:c r="E40" s="12" t="str">
-        <x:v>Drive file ID 1RejG__2xMqZe9dvY65BEP1EcjkxLdY4e; modified 2026-09-16T18:06Z
-Limit: Derivative source: the underlying Claude chat and Kees's original messages are not accessible; only this extraction and its README were supplied. Not independent corroboration of the manifest.</x:v>
-      </x:c>
-      <x:c r="F40" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="48" hidden="0" customHeight="1">
-      <x:c r="A41" s="6" t="str">
-        <x:v>EVD-recqqvvob4zYQpR8V</x:v>
-      </x:c>
-      <x:c r="B41" s="6" t="str">
-        <x:v>Drive — SHI-0001_box_level_extract (source Airtable).xlsx — read-only extract 16 Sep 2026 from appK7t991PYJ2u0DO: 33 handling units, 1,008 boxes + 51 bags, 15,770 kg; HW 9,400 (incl. 510 loose) / NR 6,370; 87 logistics units</x:v>
-      </x:c>
-      <x:c r="C41" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recqqvvob4zYQpR8V</x:v>
-      </x:c>
-      <x:c r="D41" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq/view</x:v>
-      </x:c>
-      <x:c r="E41" s="12" t="str">
-        <x:v>Drive file ID 1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq; modified 2026-09-16T20:23Z; extract states source base appK7t991PYJ2u0DO, extracted 2026-09-16, read-only
-Limit: Airtable records include advance entry, live entry and retroactive reconstruction; not independent of the manifest they generated. Pro-rata unit weights are derived, not measured.</x:v>
-      </x:c>
-      <x:c r="F41" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="48" hidden="0" customHeight="1">
-      <x:c r="A42" s="6" t="str">
-        <x:v>EVD-rec7gntN5pp4IKN6R</x:v>
-      </x:c>
-      <x:c r="B42" s="6" t="str">
-        <x:v>Airtable appK7t991PYJ2u0DO — Shipments record SHI-0001 (recruDh6qlSuJQIKP): pickup 2026-05-30, shipment 2026-07-04, status loaded; goods picked up Saturday, stored by Enrico/Pete, shipped 4 Jul</x:v>
-      </x:c>
-      <x:c r="C42" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec7gntN5pp4IKN6R</x:v>
-      </x:c>
-      <x:c r="D42" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E42" s="12" t="str">
-        <x:v>appK7t991PYJ2u0DO / tbl6RqsfwYQwcmBdF / recruDh6qlSuJQIKP (created 2026-05-28T12:47Z); consignments recVSSJpwfHpTuT2q (NR), recRr3wKcf8JBNWVD (HW)
-Limit: Read from the legacy active-data base on Kees's explicit grant (16–17 Sep); base is non-production; record may have been edited after the events; no revision history read.</x:v>
-      </x:c>
-      <x:c r="F42" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="48" hidden="0" customHeight="1">
-      <x:c r="A43" s="6" t="str">
-        <x:v>EVD-recixLbfaLKkFOS01</x:v>
-      </x:c>
-      <x:c r="B43" s="6" t="str">
-        <x:v>Airtable appK7t991PYJ2u0DO — Shipments record SHI-0002 (recAEImvwmSm1r1Nz): planned, 2026-06-23, Makariv; 'Truck to Makariv / Zhyotomir. Meant for summercamp and shipping H4U'; only one consignment record (HW)</x:v>
-      </x:c>
-      <x:c r="C43" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recixLbfaLKkFOS01</x:v>
-      </x:c>
-      <x:c r="D43" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E43" s="12" t="str">
-        <x:v>appK7t991PYJ2u0DO / tbl6RqsfwYQwcmBdF / recAEImvwmSm1r1Nz (created 2026-06-19T08:58Z); consignment rec7wrwS5dLDZh0sD (SHI-0002 — HW)
-Limit: Non-production legacy base read on explicit grant; status field not maintained after loading; SHI-0003 is absent from this base.</x:v>
-      </x:c>
-      <x:c r="F43" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="36" hidden="0" customHeight="1">
-      <x:c r="A44" s="6" t="str">
-        <x:v>EVD-recil3LS2XJuZl9kZ</x:v>
-      </x:c>
-      <x:c r="B44" s="6" t="str">
-        <x:v>Drive — SHI-0003_package README.txt — August truck: carrier Stichting Dopomoha, DAF XF 480 FT AI8800HM + Schmitz trailer AA7888XS, driver Novitskyi Vladyslav; 20 pallets / 813 boxes / 10,290 kg; drop-off points and end recipients deliberately kept off paper</x:v>
-      </x:c>
-      <x:c r="C44" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recil3LS2XJuZl9kZ</x:v>
-      </x:c>
-      <x:c r="D44" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1nmAPtYzhWIpLeHdftSsSNY_cHose4Xpq/view</x:v>
-      </x:c>
-      <x:c r="E44" s="12" t="str">
-        <x:v>Drive file ID 1nmAPtYzhWIpLeHdftSsSNY_cHose4Xpq; modified 2026-09-16T19:58Z
-Limit: Package README written after the fact (16 Sep); the 80 MB source zip could not be processed through the Drive connector.</x:v>
-      </x:c>
-      <x:c r="F44" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="48" hidden="0" customHeight="1">
-      <x:c r="A45" s="6" t="str">
-        <x:v>EVD-recUadXZjYAGon1Bt</x:v>
-      </x:c>
-      <x:c r="B45" s="6" t="str">
-        <x:v>Drive — SHI-0003_detailed_contents.xlsx — August truck pallet-by-pallet contents from 17 pallet-label photos + prior handoff: NR pallets 1–5 hospital supplies 164 boxes / 1,511 kg; HW pallets 6–20 649 boxes / 8,779 kg</x:v>
-      </x:c>
-      <x:c r="C45" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recUadXZjYAGon1Bt</x:v>
-      </x:c>
-      <x:c r="D45" s="11" t="str">
-        <x:v>https://drive.google.com/file/d/1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky/view</x:v>
-      </x:c>
-      <x:c r="E45" s="12" t="str">
-        <x:v>Drive file ID 1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky; modified 2026-09-16T19:58Z; photos folder 1FipL_kKif52APTZBFIO8_hYvmyAIgLSG (17 JPEGs, EXIF IMG_5833–5861)
-Limit: Internal reference document, not a shipping document; contents inferred from box exteriors; underlying chat and handoff.md not supplied.</x:v>
-      </x:c>
-      <x:c r="F45" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="36" hidden="0" customHeight="1">
-      <x:c r="A46" s="6" t="str">
-        <x:v>EVD-recdQv493Ry8o5y3d</x:v>
-      </x:c>
-      <x:c r="B46" s="6" t="str">
-        <x:v>Airtable appivZyJTh5tQv1On — Warehouse_Inventory_Observations, session '2026-09-02 — Kees warehouse inventory' (25 observations): goods physically in the DCA warehouse on 2 Sep 2026</x:v>
-      </x:c>
-      <x:c r="C46" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdQv493Ry8o5y3d</x:v>
-      </x:c>
-      <x:c r="D46" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E46" s="12" t="str">
-        <x:v>appivZyJTh5tQv1On / tbl6rQmwjUZsrkllO; 25 records WIO-rec6diHrx2DMbh3FC … WIO-recxToaONaYpR72kO created 2026-09-07T00:33–00:34Z; observed_by Kees; record_status current
-Limit: Approximate counts; no weights; warehouse_location links not read; records entered five days after the session.</x:v>
-      </x:c>
-      <x:c r="F46" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="60" hidden="0" customHeight="1">
-      <x:c r="A47" s="6" t="str">
-        <x:v>EVD-recJTH9lXBSM03K14</x:v>
-      </x:c>
-      <x:c r="B47" s="6" t="str">
-        <x:v>Slack huddle note F0C2F1HL7L1 — Anja–Kees huddle 16 Sep 2026 20:58–21:27 CEST (AI notes): Kees has data from all shipments except two January shipments from Lithuania and one armoured-car shipment [2:20]; method and source-supply agreements</x:v>
-      </x:c>
-      <x:c r="C47" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recJTH9lXBSM03K14</x:v>
-      </x:c>
-      <x:c r="D47" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E47" s="12" t="str">
-        <x:v>Slack file F0C2F1HL7L1 (created 2026-09-16 21:28:04 CEST); transcript file F0C2B53A99U (application/vnd.slack-huddle-transcript, 1.2 MB); huddle message https://dcau.slack.com/archives/D0AJR8SJLMQ/p1789585078919509
-Limit: AI-generated note; the underlying transcript F0C2B53A99U is not readable through this connector (unsupported file type), so timestamps and wording are as summarised.</x:v>
-      </x:c>
-      <x:c r="F47" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="36" hidden="0" customHeight="1">
-      <x:c r="A48" s="6" t="str">
-        <x:v>EVD-recdDE2xp8ht4aJ8R</x:v>
-      </x:c>
-      <x:c r="B48" s="6" t="str">
-        <x:v>Slack #logistics — Bas, 17 Aug 2026 19:18 CEST: full truck to Kharkiv Thu/Fri for €4,600 total (no VAT); DCA ~20 pallets → €2,800; Wilfred fills the rest; another drop-off location before Kyiv (H4U)</x:v>
-      </x:c>
-      <x:c r="C48" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdDE2xp8ht4aJ8R</x:v>
-      </x:c>
-      <x:c r="D48" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E48" s="12" t="str">
-        <x:v>C037X71FME0; message 2026-08-17 19:18:02 CEST (ts not returned by search tool); follow-ups Bas 18 Aug 10:02, James 18 Aug 11:18 (Lena: next week €4,700)
-Limit: Search-result excerpt truncated; message ts not captured; price is a quote, not an invoice.</x:v>
-      </x:c>
-      <x:c r="F48" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="48" hidden="0" customHeight="1">
-      <x:c r="A49" s="6" t="str">
-        <x:v>EVD-recC9dOzCgXbRSQEm</x:v>
-      </x:c>
-      <x:c r="B49" s="6" t="str">
-        <x:v>Slack #logistics — Kees, 21 Aug 2026 08:49 / 13:03 / 16:00 CEST: documents for the truck, loading ~10:00; fully loaded, driver redistributing weight, 'everything is in there'; 'Truck was sent after a long day'</x:v>
-      </x:c>
-      <x:c r="C49" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recC9dOzCgXbRSQEm</x:v>
-      </x:c>
-      <x:c r="D49" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E49" s="12" t="str">
-        <x:v>C037X71FME0; messages 2026-08-21 08:49:22, 13:03:12, 16:00:13 CEST (ts not returned by search tool); preceding: Kees 19 Aug 11:02 #marketing 'load a truck tomorrow afternoon or Friday'; Kees 20 Aug 13:48 'Truck will not be able to come today… Likely tomorrow'; James 21 Aug 09:30 asks driver name/passport/phone/plates for declaration
-Limit: Message ts values not captured; attached documents not enumerated.</x:v>
-      </x:c>
-      <x:c r="F49" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="60" hidden="0" customHeight="1">
-      <x:c r="A50" s="6" t="str">
-        <x:v>EVD-recHgOgGg8Rdr638M</x:v>
-      </x:c>
-      <x:c r="B50" s="6" t="str">
-        <x:v>Slack #logistics — 23–30 Aug 2026: Kees 'expected to arrive on wednesday' (23 Aug); James 'the truck crossed the border yesterday' (24 Aug); Kees 'Truck will be in Kharkiv tomorrow' (25 Aug); Bas 'The truck successfully has been unload it both places' (30 Aug)</x:v>
-      </x:c>
-      <x:c r="C50" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recHgOgGg8Rdr638M</x:v>
-      </x:c>
-      <x:c r="D50" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E50" s="12" t="str">
-        <x:v>C037X71FME0; Kees 2026-08-23 08:06:12; James 2026-08-24 10:55:43; Kees 2026-08-25 07:25:36; Bas 2026-08-30 11:05:46 CEST (ts not returned); Reality Watch bot 24 Aug 13:10 (plan Zhytomyr tomorrow, Kharkiv Wednesday) and 29 Aug 08:11 (truck ≠ Mission 39; unloading not yet confirmed) are derivative
-Limit: Second-hand reports; no consignee receipt, photo or signed CMR processed; Bas's source for the unloading is not stated.</x:v>
-      </x:c>
-      <x:c r="F50" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="48" hidden="0" customHeight="1">
-      <x:c r="A51" s="6" t="str">
-        <x:v>EVD-reclmhgQ3jzfn9gU2</x:v>
-      </x:c>
-      <x:c r="B51" s="6" t="str">
-        <x:v>Slack DM Kees–James — James, 23 Jun 2026 09:16 &amp; 13:30 CEST: 'H4U unloading in Zhytomir, CMR for Help Window as usually. Olga agreed'; sweets → children's camp by New Time, TVs → Lifeline (both Kyiv); Vova unloads in Makariv, truck will not go to Kyiv</x:v>
-      </x:c>
-      <x:c r="C51" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reclmhgQ3jzfn9gU2</x:v>
-      </x:c>
-      <x:c r="D51" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E51" s="12" t="str">
-        <x:v>D0AC3M2J5QE; James 2026-06-23 09:16:04 and 13:30:52 CEST; related James 2026-06-17 10:55:56 ('pallets in Makariv will be downloaded by hands like in Zhytomir by boys… how to unload those tvs so we don't need to send the truck to Kyiv') (ts not returned by search tool)
-Limit: Instruction before loading; states intended handling, not confirmation of execution; message ts not captured.</x:v>
-      </x:c>
-      <x:c r="F51" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="24" hidden="0" customHeight="1">
-      <x:c r="A52" s="6" t="str">
-        <x:v>EVD-recANxlI6i696JKG8</x:v>
-      </x:c>
-      <x:c r="B52" s="6" t="str">
-        <x:v>Slack #logistics — James, 19 May 2026 09:30 CEST: 'Palet number 6 with food for Kamyonka got broken and lose while unloading in HW warehouses… everything was dry'</x:v>
-      </x:c>
-      <x:c r="C52" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recANxlI6i696JKG8</x:v>
-      </x:c>
-      <x:c r="D52" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E52" s="12" t="str">
-        <x:v>C037X71FME0; James 2026-05-19 09:30:12 CEST (ts not returned by search tool)
-Limit: Second-hand report by James; no receipt document; ts not captured.</x:v>
-      </x:c>
-      <x:c r="F52" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="48" hidden="0" customHeight="1">
-      <x:c r="A53" s="6" t="str">
-        <x:v>EVD-recxvO3KFoot8GwOE</x:v>
-      </x:c>
-      <x:c r="B53" s="6" t="str">
-        <x:v>Slack #logistics — James, 24 Mar 2026 09:34 CEST: recipients 'very happy with the pillows and blankets'; 'with last transport they went through so many hands, that many plastic bags were trash'; send bedding to the organisation unloading first (HW or NR) or to Ludmila</x:v>
-      </x:c>
-      <x:c r="C53" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recxvO3KFoot8GwOE</x:v>
-      </x:c>
-      <x:c r="D53" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E53" s="12" t="str">
-        <x:v>C037X71FME0; James 2026-03-24 09:34:50 CEST; follow-up 09:38:55 (request for a Drive folder for loading/unloading photos and videos) (ts not returned by search tool)
-Limit: Second-hand; 'last transport' presumed to be the 10 Mar truck by date; the unloading media themselves were not located.</x:v>
-      </x:c>
-      <x:c r="F53" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="36" hidden="0" customHeight="1">
-      <x:c r="A54" s="6" t="str">
-        <x:v>EVD-recrxfCCX5DKZ9SvY</x:v>
-      </x:c>
-      <x:c r="B54" s="6" t="str">
-        <x:v>Slack group DM Bas/James/Kees — Kees, 6 Jul 2026 17:05 CEST: drivers want lunch with Igor and Olga after unloading at HW warehouse, then drive towards Kyiv; plus Bas 1 Jul #logistics schedule (depart Sat 08:00, overnight Poland, Sunday border) and James 20 Jul price €3,900 + €50 Zhytomyr</x:v>
-      </x:c>
-      <x:c r="C54" s="11" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recrxfCCX5DKZ9SvY</x:v>
-      </x:c>
-      <x:c r="D54" s="12" t="str">
-        <x:v>No direct URL recorded; use evidence record/reference</x:v>
-      </x:c>
-      <x:c r="E54" s="12" t="str">
-        <x:v>Group DM: James 2026-07-06 12:23:11 ('prepare for leading them from to 1 unloading and to 2 unloading'); Kees 2026-07-06 17:05:20 CEST. #logistics: Bas 2026-07-01 19:34:58; James 2026-07-20 12:30:32 CEST (ts not returned)
-Limit: Plans and phone reports; no unloading confirmation document; ts not captured.</x:v>
-      </x:c>
-      <x:c r="F54" s="12" t="str">
-        <x:v>Additional run evidence — incorporation pending</x:v>
-      </x:c>
-    </x:row>
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Q-H</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">James</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="str">
+        <x:v>Ambulances: the March discussion planned several deliveries, while the April report says “two ambulances delivery”. Which vehicles actually arrived during 6–17 Apr, and what did that entry include? Clarify the historical reporting scope; no new valuation or accounting policy is requested.</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ROB-recR0aCTKpJQY7a1T</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1"/>
+    <x:row r="9" ht="24" customHeight="1"/>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -10635,429 +10681,1406 @@
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" customWidth="1"/>
-    <x:col min="2" max="2" width="60" customWidth="1"/>
-    <x:col min="3" max="3" width="54" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="95" customWidth="1"/>
+    <x:col min="3" max="3" width="54" customWidth="1"/>
+    <x:col min="4" max="4" width="48" customWidth="1"/>
+    <x:col min="5" max="5" width="80" customWidth="1"/>
+    <x:col min="6" max="6" width="36" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">object_id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
+    <x:row r="1" ht="15" customHeight="1">
+      <x:c r="A1" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">evidence_id</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="4" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">display_name</x:t>
         </x:is>
       </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>airtable_object_url</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="C1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">airtable_evidence_url</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">original_source_url</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">source_reference / access limit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">snapshot_scope</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="36" hidden="0" customHeight="1">
       <x:c r="A2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-rec1A3tgId8npy6eE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-01 January truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec1A3tgId8npy6eE</x:v>
+          <x:t xml:space="preserve">EVD-recP2w8kARM0FjW3e</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="str">
+        <x:v>Drive — Goods reconstruction folder README (Kees, 16 Sep 2026) — folder structure and source roles</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recP2w8kARM0FjW3e</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Drive file 1ZdoOgAA8GJXn_3MNPzKAFceea1pu_1l9; modified 2026-09-16T20:44:43Z. Folder created 2026-09-16T21:51Z with subfolders Truck info (01 Jan, 02 Mar, 03 May, 04 Jun, 05 Jul, 06 Aug), Missions (van) (33, 34, 35, 36, 38, 39), Earlier valuations.</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="24" hidden="0" customHeight="1">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recclQ34CTtgzne9g</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-02 Jan food gap artefact</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recclQ34CTtgzne9g</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-reck3RM4FAhiKan1j</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="str">
+        <x:v>Drive — DCA-Goods-Reconstruction-Notes-for-Kees.md (Anja, 16 Sep 2026) — source-supply instructions and boundaries</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reck3RM4FAhiKan1j</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="12" t="str">
+        <x:v>Drive file 1KVawWMA2Qk4ebcYfZ89AFkfpJz_oxxm5; modified 2026-09-16T21:03:59Z</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" hidden="0" customHeight="1">
       <x:c r="A4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recQHyIOyozXotKBh</x:t>
+          <x:t xml:space="preserve">EVD-recOfWtk5eGnuCqd2</x:t>
         </x:is>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>G-03 January carry-over candidates; identities unconfirmed</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recQHyIOyozXotKBh</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="24" hidden="0" customHeight="1">
+        <x:v>Google Sheet — DCA_goods_reconstruction_2026_Jan-Jun (Kees + prior Claude chat) — 9 tabs, read as chat attachment</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recOfWtk5eGnuCqd2</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="12" t="str">
+        <x:v>Sheet 172U-YYZQQqc2qIebYuQeSNIHRSSdeR7H78y0F3koy-w; content read from the copy attached to this Claude chat (17 Sep 2026); tabs README, Comparison, Valuation_Status, Shipments, Goods_Lines, Rates, Open_Items, Corrections, Detail_Gaps
+Recorded source limit: Read from chat-attached copy; native sheet not opened in this run; the originating Claude chat is not readable (only the workbook survives).</x:v>
+      </x:c>
+      <x:c r="F4" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="60" hidden="0" customHeight="1">
       <x:c r="A5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recqfCoNgY3BgXINx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-04 Mission 33 load</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recqfCoNgY3BgXINx</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-reci8DsW1gdgoWPg6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="str">
+        <x:v>Drive — DCA goods delivered for 2026.xlsx (uploaded copy, mod 15 Sep 2026) — James's monthly kg/€ reporting, Sep 2025–Aug 2026, Jan–Jun total 98,162 kg / €782,199</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reci8DsW1gdgoWPg6</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1OC5vrenD58ewHgy7cKCbKrFRDvygpcNR/view</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>Drive file 1OC5vrenD58ewHgy7cKCbKrFRDvygpcNR (copy modified 2026-09-15T15:54:41Z). Prompt names native Sheet 1h0LgqvMB_tbL4XbkoDgrGJ-o9IjwC6wmvTgwiQk0FYU and XLSX 1qqJp4rItaMq5WbIwhwR476Wit5SHZXYo — version lineage not yet established.
+Recorded source limit: Text export without cell coordinates; native Google Sheet and its revision history not yet inspected; region attribution logic is James's and is not documented in the file.</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="72" hidden="0" customHeight="1">
       <x:c r="A6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-reckOFPCVHjlD6KJF</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-05 Mission 33 timing</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/reckOFPCVHjlD6KJF</x:v>
+          <x:t xml:space="preserve">EVD-recpYmNnGlJCfftyh</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="str">
+        <x:v>Drive — Truck January 2026.xlsx — working sheet 33, HW and NR CMR sheets, Total (20 pallets / 10,036 kg)</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recpYmNnGlJCfftyh</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1ETJQCmiyKfLEQ2G_pO4xee4s1csYN-uJ/view</x:v>
+      </x:c>
+      <x:c r="E6" s="12" t="str">
+        <x:v>Drive file 1ETJQCmiyKfLEQ2G_pO4xee4s1csYN-uJ (uploaded copy, modified 2026-09-16T07:06:11Z, created in Drive 2026-09-16T21:51Z). Prompt source guide names native Sheet 1CuyHsp8J3WrI1u9dMvh2HWNEaC3-LlUlqw7Ko3WK1lc as 'Truck January 2026' — not yet compared.
+Recorded source limit: Uploaded Excel copy read through Drive text export; cell coordinates not exposed, sheet boundaries inferred; original Google Sheet and revision history not inspected; CMR PDFs (separate files) not yet compared.</x:v>
+      </x:c>
+      <x:c r="F6" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" hidden="0" customHeight="1">
       <x:c r="A7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-rec3LncyByihvWJ7w</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-06 undocumented trucks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec3LncyByihvWJ7w</x:v>
+          <x:t xml:space="preserve">EVD-reci7q8O3ccosy82w</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Truck January: Working sheet not final; Total sheet + CMR leading</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reci7q8O3ccosy82w</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="12" t="str">
+        <x:v>Drive file 1mceuLiWgz1ksglaWF1Ha_gAWPBhfqQpl; modified 2026-09-16T20:32:50Z</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" hidden="0" customHeight="1">
       <x:c r="A8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recO2rSGDV2NHLlFu</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-07 undocumented trucks contents</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recO2rSGDV2NHLlFu</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recdaLZzXrb5e9Nu1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Missing information: two January trucks from Lithuania (mattresses)</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdaLZzXrb5e9Nu1</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="12" t="str">
+        <x:v>Drive file 1uJ8cnQ6yZVwAJ-siXR05AWSDABZCujbU; modified 2026-09-16T20:30:18Z</x:v>
+      </x:c>
+      <x:c r="F8" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="84" hidden="0" customHeight="1">
       <x:c r="A9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-rec2SXYOAnOati9oQ</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-08 region convention</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec2SXYOAnOati9oQ</x:v>
+          <x:t xml:space="preserve">EVD-recuxxn3mlOO1aDUI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="str">
+        <x:v>Drive — Truck March (def.) (1).xlsx — NR (7 pallets / 4,226 kg) and HW (24 pallets / 15,093 kg) CMR sheets, 10 Mar 2026</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recuxxn3mlOO1aDUI</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1DoitCvlni5TBXjRbZi5cJqxjEDv0X3oW/view</x:v>
+      </x:c>
+      <x:c r="E9" s="12" t="str">
+        <x:v>Drive file 1DoitCvlni5TBXjRbZi5cJqxjEDv0X3oW; file modified 2026-03-10T06:57:18Z. Prompt source guide names Drive copy 1B22T52KP5sWZccCTyiu9tzmi6QV-aPBW (not yet compared). Companion CMR xls in same folder: CMR Nezlamna Rodyna.xls (15F3lL001NPwMnH6TB_RzX_f_t60TS5l-, mod 2026-03-10T06:57Z), CMR Help Window.xls (1IdM0Teek8pKOFlP48hG3WZ8KcqIzAAsd, mod 2026-03-18T05:41Z) — not yet read.
+Recorded source limit: Uploaded Excel read via text export (no cell coordinates); no H4U tab present although Kees's reconstruction cites an 'H4U tab' for pallets 7, 8, 11, 15, 19, 32 — that source is not in the supplied file. Companion CMR .xls files not yet read.</x:v>
+      </x:c>
+      <x:c r="F9" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" hidden="0" customHeight="1">
       <x:c r="A10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recl6gIk4jwSbqm6p</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-09 March truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recl6gIk4jwSbqm6p</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recXV9ispSK3XyfXd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — WhatsApp screenshots: pallet numbers do not match CMR; match by content or leave unresolved</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recXV9ispSK3XyfXd</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="12" t="str">
+        <x:v>Drive file 1cP1gg5-d6DEjaaKqEHOJLgOrzlHbg_5U; modified 2026-09-16T20:39:54Z</x:v>
+      </x:c>
+      <x:c r="F10" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recWORLSXcsZPpKOQ</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-10 March sheet inconsistencies</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recWORLSXcsZPpKOQ</x:v>
+          <x:t xml:space="preserve">EVD-recCEC5J1MVeGwWQb</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="str">
+        <x:v>WhatsApp screenshot 1/3 — Kees pallet notes #32–#39 (Feb 2026 packing for March truck)</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recCEC5J1MVeGwWQb</x:v>
+      </x:c>
+      <x:c r="D11" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="12" t="str">
+        <x:v>Drive file 1rdJo4Iv5NFOcMjS-aOpEBZIkmAPV1N-T (945×2048 px); screenshot taken 2026-09-16 11:17 (device clock); WhatsApp search box shows 'Februa'; result counter '1 van 5 resultaten'
+Recorded source limit: Screenshot only: no dates, no chat name, no recipient, partial last message; original chat export not supplied.</x:v>
+      </x:c>
+      <x:c r="F11" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" hidden="0" customHeight="1">
       <x:c r="A12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-rec0W2XImFq9vN3CP</x:t>
+          <x:t xml:space="preserve">EVD-recdkvcEAnpQD59Sm</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="2" t="str">
-        <x:v>G-11 WhatsApp candidate matches; 14-vs-15 box conflict unresolved</x:v>
-      </x:c>
-      <x:c r="C12" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec0W2XImFq9vN3CP</x:v>
+        <x:v>WhatsApp screenshot 2/3 — Kees pallet notes #38–#43 incl. H4U pallets (Feb 2026)</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdkvcEAnpQD59Sm</x:v>
+      </x:c>
+      <x:c r="D12" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="12" t="str">
+        <x:v>Drive file 1n7lyb989GVI_VhiGw1QcKMuzvZnt776z; screenshot 2026-09-16 11:18; search 'Februa'
+Recorded source limit: Screenshot only; no dates; overlaps screenshot 3 for 15:43–17:07 messages.</x:v>
+      </x:c>
+      <x:c r="F12" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" hidden="0" customHeight="1">
       <x:c r="A13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recB37f26Q14iwW6a</x:t>
+          <x:t xml:space="preserve">EVD-recd4zaJNUefVVHrt</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="2" t="str">
-        <x:v>G-12 March H4U attribution; candidate links, planning tab absent from snapshot</x:v>
-      </x:c>
-      <x:c r="C13" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recB37f26Q14iwW6a</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" hidden="0" customHeight="1">
+        <x:v>WhatsApp screenshot 3/3 — Kees pallet notes #44–#46 (Feb 2026)</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recd4zaJNUefVVHrt</x:v>
+      </x:c>
+      <x:c r="D13" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="12" t="str">
+        <x:v>Drive file 1QbNhcb7fmrPRO7cr_qVp9CM2VmUFXdaB; screenshot 2026-09-16 11:18; search 'Februa'
+Recorded source limit: Screenshot only; at least one message after #46 not captured.</x:v>
+      </x:c>
+      <x:c r="F13" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="96" hidden="0" customHeight="1">
       <x:c r="A14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recnh2w8NfAksexUL</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-13 Mission 34</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recnh2w8NfAksexUL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recDe227kjiqwpZc5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="str">
+        <x:v>Drive — Def. Truck May 6 2026.xlsx (uploaded copy) — HW 16 pallets / 8,700 kg incl. H4U Ludmila/Zhytomir pallets 1–4; NR 4 pallets / 1,510 kg; total 806 boxes / 10,210 kg</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recDe227kjiqwpZc5</x:v>
+      </x:c>
+      <x:c r="D14" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="12" t="str">
+        <x:v>Drive file 1TVO8UH7ynwxAIP-qKU9I9Ll00DumkmC1 (uploaded copy modified 2026-09-16T14:55:04Z). Same underlying workbook as prompt-named native Sheet 1wMyxL1e_KNzUj1N__pmcC2lHHd1mIjF1_RReIHB8viQ and as prior-run Evidence EVD-recf68zLDBfKnZf0A / EVD-rec340ub5uaSKcVJE (RUN-rechGOzgthgfAGzZu) — not independent corroboration. Companions in folder: Truck May .xlsx (1Bk2CLJaI1ZAq7lzKPPCeqYEcX1cyiBym), Truck May 6 2026 (1).xlsx (1-5Qy59-YD01_FWvaNBT_T87xXiUm3yH-, mod 2026-05-06T01:50Z), CMR Nezlamna Rodyna May 2026.xls (11gbNZ7OjOoUnZNYYpWMk-2vtAdvb_MC2) — not yet read.
+Recorded source limit: Text export flattens sheets; cell references reconstructed from row order. Truck May .xlsx working version and CMR xls not yet compared.</x:v>
+      </x:c>
+      <x:c r="F14" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="60" hidden="0" customHeight="1">
       <x:c r="A15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recR0aCTKpJQY7a1T</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-14 Mission 35</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recR0aCTKpJQY7a1T</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recjovJhHNHrkGZb3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="str">
+        <x:v>Drive — Manifest_SHI-0002_Total kopie.pdf — June truck 24 Jun 2026, Zhytomyr/Makariv, 437 boxes / 7,570.5 kg (HW 3,745.5; Salim 3,632; Lifeline 193)</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recjovJhHNHrkGZb3</x:v>
+      </x:c>
+      <x:c r="D15" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="12" t="str">
+        <x:v>Drive file 1d0t1DS4q3HbHXmb0r2FvYsNNLvMHQuuq (file modified 2026-06-24T08:44:15Z). Copies of the same manifest set exist in the operational June Documents folder (1ljdisl-eBtNJvDlWflx2bgoQH0QItdkY) and the Manifest 2026 bundle — not independent sources. Companions: Manifest_SHI-0002_HW/Salim/Lifeline kopie.pdf, 1. Detailed_Manifest_SHI-0002 kopie.xlsx (1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM), SHI-0002_pallet_detail_extraction.xlsx — not yet read.</x:v>
+      </x:c>
+      <x:c r="F15" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" hidden="0" customHeight="1">
       <x:c r="A16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recQVOExvYChyUyHG</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-15 May truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recQVOExvYChyUyHG</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="24" hidden="0" customHeight="1">
+          <x:t xml:space="preserve">EVD-recsWgu6FH9FSh1AU</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="str">
+        <x:v>Drive — SHI-0002 Pallet Detail Extraction README (derived Claude output, Kees's chat) — no pallet photos exist; Monitors vs TVs on SU-0011 unresolved</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recsWgu6FH9FSh1AU</x:v>
+      </x:c>
+      <x:c r="D16" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="12" t="str">
+        <x:v>Drive file 1nyEZIRg9_1aS3DK9_pf6W6jfPhL2Ngyz (modified 2026-09-16T18:07:10Z). Derived from a Claude chat about SHI-0002 ('Shipment 0002 pallet organization'); the underlying chat is not accessible to this run.
+Recorded source limit: AI-generated summary of an inaccessible chat; the companion xlsx and 'other_documents' folder not yet read.</x:v>
+      </x:c>
+      <x:c r="F16" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" hidden="0" customHeight="1">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recFkYkFT1rMJPJ6n</x:t>
+          <x:t xml:space="preserve">EVD-rec3AuCzNvlH0aA5H</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>G-16 May reporting: proposed duplication/omission reading</x:v>
-      </x:c>
-      <x:c r="C17" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recFkYkFT1rMJPJ6n</x:v>
+        <x:v>Drive — Manifest_SHI-0001..pdf (driver &amp; customs manifest) — July truck dispatch 4 Jul 2026, Kharkiv, 32 pallets / 1,008 boxes / 15,260 kg + 51 bags bedding 510 kg loose</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec3AuCzNvlH0aA5H</x:v>
+      </x:c>
+      <x:c r="D17" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="12" t="str">
+        <x:v>Drive file 1w1A4r0GgTIeLfYNt5EaBPPOSMshgQ-wH (modified 2026-09-16T17:22:37Z). Prompt names operational copy '5. July Manifest_SHI-0001..pdf' 1Y7cDxT_pEvPKmoQF1Ac0OnKV3I-nYnLL — same document, not independent. CMR PDFs in folder: CMR_SHI-0001_HW kopie.pdf (1ijQJZlohLI3aLLgr19OayewgfHHBIFCJ), CMR_SHI-0001_NR kopie.pdf (1pwtjruY-5V3E34zvcUKhUc4aXlfkS6e8), both modified 2026-06-27 — not yet read.</x:v>
+      </x:c>
+      <x:c r="F17" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="24" hidden="0" customHeight="1">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recjIzGNdwLJfju2W</x:t>
+          <x:t xml:space="preserve">EVD-reccKtLmFYdcbgiig</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="2" t="str">
-        <x:v>G-17 Mission 36: 507 kg stated / 527 kg line sum; unresolved</x:v>
-      </x:c>
-      <x:c r="C18" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recjIzGNdwLJfju2W</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="24" hidden="0" customHeight="1">
+        <x:v>Drive — Manifest_SHI-0001_detail.pdf (internal detailed manifest) — July truck subcategory detail per pallet, HW 19 / NR 13 pallets</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reccKtLmFYdcbgiig</x:v>
+      </x:c>
+      <x:c r="D18" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="12" t="str">
+        <x:v>Drive file 1t3ygcUmwXe9sXtFtnovOx5ATrp6Tt-EX (file modified 2026-06-26T19:30:26Z). Companion Airtable extract: SHI-0001_box_level_extract (source Airtable).xlsx (1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq) — not yet read.</x:v>
+      </x:c>
+      <x:c r="F18" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="84" hidden="0" customHeight="1">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recOiUWgo6VxgCpGs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-18 June truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recOiUWgo6VxgCpGs</x:v>
+          <x:t xml:space="preserve">EVD-rec0F392MGFzyMkvY</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="2" t="str">
+        <x:v>Drive — Loading_list_SHI-0003.pdf — August truck, list dated 20 Aug 2026, Kharkiv: HW 15 pallets / 649 boxes / 8,779 kg; NR 5 pallets / 164 boxes / 1,511 kg</x:v>
+      </x:c>
+      <x:c r="C19" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec0F392MGFzyMkvY</x:v>
+      </x:c>
+      <x:c r="D19" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="12" t="str">
+        <x:v>Drive file 1W8-8AgC55oirp0T4B97S5gGrWbeT5k4q (modified 2026-09-16T19:58:03Z). Companions: Loading_list_SHI-0003.xlsx (1pLz1ERu47AFPmxA5YioIx3kFXLkn1mGK), SHI-0003_detailed_contents.xlsx (1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky), CMR_SHI-0003_HW.pdf (1Mjxce9QNTf9T1B2eqm-od6wWwqCpCpXg), CMR_SHI-0003_NR.pdf (1uZwO3DwNOdqMJOwlmT_KYNCZJodG0Lr6), 17 pallet photos in '02 Source photos' (1FipL_kKif52APTZBFIO8_hYvmyAIgLSG), 'Source data SHI-0003_package.zip' 80 MB (1mDd0-el_ID7zjmUbazsDvYSYBRxOjSRf) — companions not yet read; zip not processable through the Drive connector.</x:v>
+      </x:c>
+      <x:c r="F19" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" hidden="0" customHeight="1">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recefuxSdBFM8PkuY</x:t>
+          <x:t xml:space="preserve">EVD-reczExBGAKskkWAOy</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="str">
-        <x:v>G-19 June reporting: proposed 148 kg duplication explanation</x:v>
-      </x:c>
-      <x:c r="C20" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recefuxSdBFM8PkuY</x:v>
+        <x:v>Kees note (16 Sep 2026) — Mission 33 armoured van: no loading list; from memory mostly second-hand clothing (~700 kg per James)</x:v>
+      </x:c>
+      <x:c r="C20" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reczExBGAKskkWAOy</x:v>
+      </x:c>
+      <x:c r="D20" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="12" t="str">
+        <x:v>Drive file 1xye4e8GiGtAIZsSNiSxupfVuBBVZX0US; modified 2026-09-16T21:39:25Z</x:v>
+      </x:c>
+      <x:c r="F20" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" hidden="0" customHeight="1">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recizQEts3O2pYoJn</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-20 June handover</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recizQEts3O2pYoJn</x:v>
+          <x:t xml:space="preserve">EVD-recQPFCLknLS7NRoI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Mission 34 (Feb): 13 Nutridrink boxes 260 kg confirmed; earlier price statements</x:v>
+      </x:c>
+      <x:c r="C21" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recQPFCLknLS7NRoI</x:v>
+      </x:c>
+      <x:c r="D21" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="12" t="str">
+        <x:v>Drive file 1ARFYAIZzkDqhrFdOgJRr2tHYvFQgiUzG; modified 2026-09-16T21:50:43Z
+Recorded source limit: No original loading list for Mission 34 supplied; note is a recollection.</x:v>
+      </x:c>
+      <x:c r="F21" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="24" hidden="0" customHeight="1">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-rec5K5YO2pTOqSbFb</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-21 July truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/rec5K5YO2pTOqSbFb</x:v>
+          <x:t xml:space="preserve">EVD-recDpcZyE0q3nqz4p</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Mission 35 (6 Apr) loading list as given: 6 lines, 686 kg, mostly Lighthouse Makariv</x:v>
+      </x:c>
+      <x:c r="C22" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recDpcZyE0q3nqz4p</x:v>
+      </x:c>
+      <x:c r="D22" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="12" t="str">
+        <x:v>Drive file 1maR4s1f-b6_YzrsxZtA9xUy_obomXtGa; modified 2026-09-16T21:39:54Z
+Recorded source limit: Original loading list document not supplied; transcription by Kees.</x:v>
+      </x:c>
+      <x:c r="F22" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="24" hidden="0" customHeight="1">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recDmbeTI4kj1LGMs</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-22 Mission 37 terminology</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recDmbeTI4kj1LGMs</x:v>
+          <x:t xml:space="preserve">EVD-recRp4HzSsJj4FwZ5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Mission 36 (24 May) list of goods as given: 7 lines, 64 units, 507 kg</x:v>
+      </x:c>
+      <x:c r="C23" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recRp4HzSsJj4FwZ5</x:v>
+      </x:c>
+      <x:c r="D23" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="12" t="str">
+        <x:v>Drive file 1g4CqV1AS7a8JMG6OJru3rdfck2kNadc8; modified 2026-09-16T21:41:32Z
+Recorded source limit: Original list not supplied; transcription.</x:v>
+      </x:c>
+      <x:c r="F23" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" hidden="0" customHeight="1">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recctSkY9s9OWX9N2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-23 July truck absent/understated</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recctSkY9s9OWX9N2</x:v>
+          <x:t xml:space="preserve">EVD-reckPmE5zeLQ5sBhj</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="2" t="str">
+        <x:v>Kees note (16 Sep 2026) — Mission 38 (11–21 Jul) loading list sent to James 10 Jul: 55 boxes medical food 510 kg + 2 boxes food 15 kg</x:v>
+      </x:c>
+      <x:c r="C24" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reckPmE5zeLQ5sBhj</x:v>
+      </x:c>
+      <x:c r="D24" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="12" t="str">
+        <x:v>Drive file 1V-YWm2JDtbz78aHWY75m8zTua3bkepZr; modified 2026-09-16T21:48:10Z
+Recorded source limit: The 10 Jul message to James not yet located in Slack/Gmail.</x:v>
+      </x:c>
+      <x:c r="F24" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="24" hidden="0" customHeight="1">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recj1ALxy6QQ0ajdE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-24 Mission 38</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recj1ALxy6QQ0ajdE</x:v>
+          <x:t xml:space="preserve">EVD-recHxzwdLF80ShqFA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="2" t="str">
+        <x:v>Drive — Mission_39_Loading_List.pdf — van loading list prepared for James, 20 Aug 2026: 8 lines, 167 units, 1,286 kg</x:v>
+      </x:c>
+      <x:c r="C25" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recHxzwdLF80ShqFA</x:v>
+      </x:c>
+      <x:c r="D25" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="12" t="str">
+        <x:v>Drive file 1pTtMGm8LcUJs4To6V0zaOxxQqqsa_FIV; modified 2026-09-16T19:42:27Z; document header 'Prepared for James | 20 August 2026'</x:v>
+      </x:c>
+      <x:c r="F25" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" hidden="0" customHeight="1">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recIOT2vNEsqCjJFp</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B26" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-25 August truck</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recIOT2vNEsqCjJFp</x:v>
+          <x:t xml:space="preserve">EVD-recMeesVNstFr8kZf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="2" t="str">
+        <x:v>Kees reference (16 Sep 2026) — Van mission prices as stated in chat (earlier evaluation, not definitive)</x:v>
+      </x:c>
+      <x:c r="C26" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recMeesVNstFr8kZf</x:v>
+      </x:c>
+      <x:c r="D26" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="12" t="str">
+        <x:v>Drive file 1bBKpvHTygpB1X3lyyQ23GnlqbhBDIVcb; modified 2026-09-16T21:50:43Z</x:v>
+      </x:c>
+      <x:c r="F26" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="24" hidden="0" customHeight="1">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recFHukYf2JtvL0Ak</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-26 Mission 39</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recFHukYf2JtvL0Ak</x:v>
+          <x:t xml:space="preserve">EVD-recT9nVfjN2snhuCi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="str">
+        <x:v>Slack #marketing — Lieke, 23 Jan 2026: December-2025 achievements — 'in a week, Bohdan received an armored van, we've sent three trucks'; 'we're preparing our next mission, mission 33'</x:v>
+      </x:c>
+      <x:c r="C27" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recT9nVfjN2snhuCi</x:v>
+      </x:c>
+      <x:c r="D27" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="12" t="str">
+        <x:v>Slack channel C037S4YL6MT; message 2026-01-23 20:58:26 CET by lieke heil (U038N98335E); message ts not captured by the search tool (limitation).</x:v>
+      </x:c>
+      <x:c r="F27" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="24" hidden="0" customHeight="1">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recTCK3iNLxzUljHh</x:t>
+          <x:t xml:space="preserve">EVD-recVH7fncxcyqfkoh</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="str">
-        <x:v>G-27 Total-tab mismatch in extracted copy; native cells not inspected</x:v>
-      </x:c>
-      <x:c r="C28" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recTCK3iNLxzUljHh</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="24" hidden="0" customHeight="1">
+        <x:v>Slack #marketing — Bas, 16 Feb 2026: truck from NL €3,500 vs truck from Lithuania €2,500 (winter/heating campaign)</x:v>
+      </x:c>
+      <x:c r="C28" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recVH7fncxcyqfkoh</x:v>
+      </x:c>
+      <x:c r="D28" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="12" t="str">
+        <x:v>Slack channel C037S4YL6MT; message 2026-02-16 14:57:24 CET by Bas (U038JKTA7QQ); ts not captured.</x:v>
+      </x:c>
+      <x:c r="F28" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="36" hidden="0" customHeight="1">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ROB-recXJEqaQUWu2GHBi</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G-28 sender address change</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" s="7" t="str">
-        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tblv7wDJZjJRs34nU/recXJEqaQUWu2GHBi</x:v>
+          <x:t xml:space="preserve">EVD-reclaxOv0x7yGfjXB</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="str">
+        <x:v>Drive doc — Emergency Appeal for Ukraine (Feb 2026 campaign): 'We have already sent 5 trucks in 2026'; two winter trucks; mission 35 on 6 April</x:v>
+      </x:c>
+      <x:c r="C29" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reclaxOv0x7yGfjXB</x:v>
+      </x:c>
+      <x:c r="D29" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="12" t="str">
+        <x:v>Google Doc 1OdP715UQCwQEvIMAKGL4sazamrxzdfDVti1XEHhkdHk; read 17 Sep 2026 (current revision; historical revision at time of posting not inspected).
+Recorded source limit: Current revision read; edits after Feb 2026 possible.</x:v>
+      </x:c>
+      <x:c r="F29" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="24" hidden="0" customHeight="1">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-reccKKxnjMSvh7bql</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="str">
+        <x:v>Slack DM Kees–James — Kees, 4 Feb 2026: take only nutrition expiring before March in the van; rest by truck end of month</x:v>
+      </x:c>
+      <x:c r="C30" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reccKKxnjMSvh7bql</x:v>
+      </x:c>
+      <x:c r="D30" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="12" t="str">
+        <x:v>Slack DM D0AC3M2J5QE; message 2026-02-04 16:14:32 CET by Kees (U0ABU10D2KD); ts not captured.</x:v>
+      </x:c>
+      <x:c r="F30" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recNRAElLXonh6n4A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="2" t="str">
+        <x:v>Slack #fundraising — James, 3 Feb 2026: 'Let's see how Bohdan does with the van first. I will check also when the van may be ready for sending to UA'</x:v>
+      </x:c>
+      <x:c r="C31" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recNRAElLXonh6n4A</x:v>
+      </x:c>
+      <x:c r="D31" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="12" t="str">
+        <x:v>Slack channel C037USZ92V8; message 2026-02-03 12:24:25 CET by James (U05DKS7C3U0); ts not captured.</x:v>
+      </x:c>
+      <x:c r="F31" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="24" hidden="0" customHeight="1">
+      <x:c r="A32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recLS1vD7QUXfGrLm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="2" t="str">
+        <x:v>Slack DM Kees–James — Kees relays H4U (Johan), 14 May 2026: offer of ~200 beds/mattresses from a residential complex in Zaandam</x:v>
+      </x:c>
+      <x:c r="C32" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recLS1vD7QUXfGrLm</x:v>
+      </x:c>
+      <x:c r="D32" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="12" t="str">
+        <x:v>Slack DM D0AC3M2J5QE; message 2026-05-14 09:14:02 CEST by Kees; ts not captured.</x:v>
+      </x:c>
+      <x:c r="F32" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="24" hidden="0" customHeight="1">
+      <x:c r="A33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recJI4FH0GVHLhByd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="2" t="str">
+        <x:v>Slack group DM Bas/James/Kees — James, 3 &amp; 6 Jul 2026: two missions at once; 'goods from last transport have not been picked up by everyone'; mission 37 = truck drivers' journey (e-toll, Polish road inspection)</x:v>
+      </x:c>
+      <x:c r="C33" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recJI4FH0GVHLhByd</x:v>
+      </x:c>
+      <x:c r="D33" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="12" t="str">
+        <x:v>Slack group DM (Bas, James, Kees); messages 2026-07-03 10:31:58 CEST and 2026-07-06 10:10:39 CEST by James (U05DKS7C3U0); ts not captured.</x:v>
+      </x:c>
+      <x:c r="F33" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="24" hidden="0" customHeight="1">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recOX5n0nZClxgYdP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="str">
+        <x:v>Slack #logistics — James &amp; Bas, 3 Jul 2026: WhatsApp group for mission 37 with the two drivers; 'they start driving at 08:00 this Saturday'</x:v>
+      </x:c>
+      <x:c r="C34" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recOX5n0nZClxgYdP</x:v>
+      </x:c>
+      <x:c r="D34" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="12" t="str">
+        <x:v>Slack channel C037X71FME0; James 2026-07-03 14:57:43 CEST; Bas reply 2026-07-03 15:07:19 CEST; ts not captured.</x:v>
+      </x:c>
+      <x:c r="F34" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="24" hidden="0" customHeight="1">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recYfz6sYRCJERXPw</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="str">
+        <x:v>Slack #ukraine — DCA Bot, 13 Sep 2026: mission dates 34–39; 'Mission 37' used for the 4 July truck and for camp fundraising (derivative AI summary)</x:v>
+      </x:c>
+      <x:c r="C35" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recYfz6sYRCJERXPw</x:v>
+      </x:c>
+      <x:c r="D35" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="12" t="str">
+        <x:v>Slack #ukraine; Dutch Civilian Action Bot message 2026-09-13 20:34:59 CEST; ts not captured.
+Recorded source limit: AI summary; underlying sources not enumerated in the message.</x:v>
+      </x:c>
+      <x:c r="F35" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="60" hidden="0" customHeight="1">
+      <x:c r="A36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recZJ8yS3SefenE0j</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="2" t="str">
+        <x:v>Gmail — Kees → W.B. van der Donk Transport, 27 Jun–3 Jul 2026: paperwork for the Kharkiv transport (two CMRs + manifest), manifest adjustment 3 Jul, confirmation letter</x:v>
+      </x:c>
+      <x:c r="C36" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recZJ8yS3SefenE0j</x:v>
+      </x:c>
+      <x:c r="D36" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="12" t="str">
+        <x:v>Gmail thread 19f0888eec7ab63d; messages 19f088c95bd1c9e9 (2026-06-27T10:07Z), 19f274c40f2c9867 (2026-07-03T09:25Z), 19f27cb22105e74c (2026-07-03T11:44Z). Related thread 19f2908cb1d871a4 'DCA Humanitarian Transport Support Letter' (2026-07-03, to info@wbvanderdonktransport.nl). Bodies read at snippet level only; attachments not opened.
+Recorded source limit: Snippets only; attachments (CMRs, manifest versions) not compared with the Drive copies.</x:v>
+      </x:c>
+      <x:c r="F36" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="24" hidden="0" customHeight="1">
+      <x:c r="A37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recibLdWHNIJanw5J</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="2" t="str">
+        <x:v>Gmail — 'DCA invoice for truck June 2026' (Kees → Tomas/finance, 6 Jul–13 Aug 2026): invoice for the truck loaded 24 June; Ukraine asking whether paid (12 Aug)</x:v>
+      </x:c>
+      <x:c r="C37" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recibLdWHNIJanw5J</x:v>
+      </x:c>
+      <x:c r="D37" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="12" t="str">
+        <x:v>Gmail thread 19f3733ade8be4d1; messages 19f3734b144bd05e (2026-07-06), 19f3bdcdfd5cc1d7 (2026-07-07, Tomas), 19ff5737c9a65542 (2026-08-12), 19ff9e45fc3ecded (2026-08-13). Snippets only; invoice attachment not opened.</x:v>
+      </x:c>
+      <x:c r="F37" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="36" hidden="0" customHeight="1">
+      <x:c r="A38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recx7hibtO7QmFOev</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="2" t="str">
+        <x:v>Gmail — 'CMR papers DCA' (Kees ↔ Olena/Elena Beresovskaya, 14–18 Aug 2026): stamped CMR needed for the carrier's bank currency check; James sent the documents 17 Aug</x:v>
+      </x:c>
+      <x:c r="C38" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recx7hibtO7QmFOev</x:v>
+      </x:c>
+      <x:c r="D38" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="12" t="str">
+        <x:v>Gmail thread 19ef5524fa59492e; messages 19ffeb7611834a00 (2026-08-14), 19ffeeaf05df6620 (2026-08-14, Olena), 1a00f520cb360848 (2026-08-17), 1a0160cda53379e3 (2026-08-18, stamped documents), 1a01631a93217beb (2026-08-18, Olena). Thread has ≥5 messages; earlier messages (thread ID dates from June) not read.</x:v>
+      </x:c>
+      <x:c r="F38" s="12" t="str">
+        <x:v>Original 37-source set</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="48" hidden="0" customHeight="1">
+      <x:c r="A39" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recN9cYuabcVyjTpP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>Drive — 1. Detailed_Manifest_SHI-0002 kopie.xlsx — June truck per-recipient detail: HW 6 pallets/236 boxes/3,745.5 kg; Salim 6/196/3,632; Lifeline 5/193; loading Noordwijkerhout 24.06.2026</x:v>
+      </x:c>
+      <x:c r="C39" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recN9cYuabcVyjTpP</x:v>
+      </x:c>
+      <x:c r="D39" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM/view</x:v>
+      </x:c>
+      <x:c r="E39" s="12" t="str">
+        <x:v>Drive file ID 1TbP4RqkwO05sdyiWTsKNExiUH8qyb7gM; file modified 2026-06-24T07:24Z; uploaded to Intake folder 2026-09-16
+Recorded source limit: Declared/planned document generated before or on loading day; not evidence of physical load or receipt. Read via Drive text export (sheet boundaries flattened).</x:v>
+      </x:c>
+      <x:c r="F39" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="36" hidden="0" customHeight="1">
+      <x:c r="A40" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recF6Tt5AAd4wB5E5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>Drive — SHI-0002_pallet_detail_extraction.xlsx (derived Claude output from Kees's June shipment chat) — LU-level detail, correction history, Monitors vs TVs conflict</x:v>
+      </x:c>
+      <x:c r="C40" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recF6Tt5AAd4wB5E5</x:v>
+      </x:c>
+      <x:c r="D40" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1RejG__2xMqZe9dvY65BEP1EcjkxLdY4e/view</x:v>
+      </x:c>
+      <x:c r="E40" s="12" t="str">
+        <x:v>Drive file ID 1RejG__2xMqZe9dvY65BEP1EcjkxLdY4e; modified 2026-09-16T18:06Z
+Recorded source limit: Derivative source: the underlying Claude chat and Kees's original messages are not accessible; only this extraction and its README were supplied. Not independent corroboration of the manifest.</x:v>
+      </x:c>
+      <x:c r="F40" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="48" hidden="0" customHeight="1">
+      <x:c r="A41" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recqqvvob4zYQpR8V</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>Drive — SHI-0001_box_level_extract (source Airtable).xlsx — read-only extract 16 Sep 2026 from appK7t991PYJ2u0DO: 33 handling units, 1,008 boxes + 51 bags, 15,770 kg; HW 9,400 (incl. 510 loose) / NR 6,370; 87 logistics units</x:v>
+      </x:c>
+      <x:c r="C41" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recqqvvob4zYQpR8V</x:v>
+      </x:c>
+      <x:c r="D41" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq/view</x:v>
+      </x:c>
+      <x:c r="E41" s="12" t="str">
+        <x:v>Drive file ID 1juwHaTRhfhil3JdiHGiwpi3JEipz_cYq; modified 2026-09-16T20:23Z; extract states source base appK7t991PYJ2u0DO, extracted 2026-09-16, read-only
+Recorded source limit: Airtable records include advance entry, live entry and retroactive reconstruction; not independent of the manifest they generated. Pro-rata unit weights are derived, not measured.</x:v>
+      </x:c>
+      <x:c r="F41" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="48" hidden="0" customHeight="1">
+      <x:c r="A42" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-rec7gntN5pp4IKN6R</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>Airtable appK7t991PYJ2u0DO — Shipments record SHI-0001 (recruDh6qlSuJQIKP): pickup 2026-05-30, shipment 2026-07-04, status loaded; goods picked up Saturday, stored by Enrico/Pete, shipped 4 Jul</x:v>
+      </x:c>
+      <x:c r="C42" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rec7gntN5pp4IKN6R</x:v>
+      </x:c>
+      <x:c r="D42" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="12" t="str">
+        <x:v>appK7t991PYJ2u0DO / tbl6RqsfwYQwcmBdF / recruDh6qlSuJQIKP (created 2026-05-28T12:47Z); consignments recVSSJpwfHpTuT2q (NR), recRr3wKcf8JBNWVD (HW)
+Recorded source limit: Read from the legacy active-data base on Kees's explicit grant (16–17 Sep); base is non-production; record may have been edited after the events; no revision history read.</x:v>
+      </x:c>
+      <x:c r="F42" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="48" hidden="0" customHeight="1">
+      <x:c r="A43" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recixLbfaLKkFOS01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>Airtable appK7t991PYJ2u0DO — Shipments record SHI-0002 (recAEImvwmSm1r1Nz): planned, 2026-06-23, Makariv; 'Truck to Makariv / Zhyotomir. Meant for summercamp and shipping H4U'; only one consignment record (HW)</x:v>
+      </x:c>
+      <x:c r="C43" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recixLbfaLKkFOS01</x:v>
+      </x:c>
+      <x:c r="D43" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="12" t="str">
+        <x:v>appK7t991PYJ2u0DO / tbl6RqsfwYQwcmBdF / recAEImvwmSm1r1Nz (created 2026-06-19T08:58Z); consignment rec7wrwS5dLDZh0sD (SHI-0002 — HW)
+Recorded source limit: Non-production legacy base read on explicit grant; status field not maintained after loading; SHI-0003 is absent from this base.</x:v>
+      </x:c>
+      <x:c r="F43" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="36" hidden="0" customHeight="1">
+      <x:c r="A44" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recil3LS2XJuZl9kZ</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>Drive — SHI-0003_package README.txt — August truck: carrier Stichting Dopomoha, DAF XF 480 FT AI8800HM + Schmitz trailer AA7888XS, driver Novitskyi Vladyslav; 20 pallets / 813 boxes / 10,290 kg; drop-off points and end recipients deliberately kept off paper</x:v>
+      </x:c>
+      <x:c r="C44" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recil3LS2XJuZl9kZ</x:v>
+      </x:c>
+      <x:c r="D44" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1nmAPtYzhWIpLeHdftSsSNY_cHose4Xpq/view</x:v>
+      </x:c>
+      <x:c r="E44" s="12" t="str">
+        <x:v>Drive file ID 1nmAPtYzhWIpLeHdftSsSNY_cHose4Xpq; modified 2026-09-16T19:58Z
+Recorded source limit: Package README written after the fact (16 Sep); the 80 MB source zip could not be processed through the Drive connector.</x:v>
+      </x:c>
+      <x:c r="F44" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="48" hidden="0" customHeight="1">
+      <x:c r="A45" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recUadXZjYAGon1Bt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>Drive — SHI-0003_detailed_contents.xlsx — August truck pallet-by-pallet contents from 17 pallet-label photos + prior handoff: NR pallets 1–5 hospital supplies 164 boxes / 1,511 kg; HW pallets 6–20 649 boxes / 8,779 kg</x:v>
+      </x:c>
+      <x:c r="C45" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recUadXZjYAGon1Bt</x:v>
+      </x:c>
+      <x:c r="D45" s="11" t="str">
+        <x:v>https://drive.google.com/file/d/1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky/view</x:v>
+      </x:c>
+      <x:c r="E45" s="12" t="str">
+        <x:v>Drive file ID 1UzaKIqLfaDTrUMUYM1nKnnh94Z3NBzky; modified 2026-09-16T19:58Z; photos folder 1FipL_kKif52APTZBFIO8_hYvmyAIgLSG (17 JPEGs, EXIF IMG_5833–5861)
+Recorded source limit: Internal reference document, not a shipping document; contents inferred from box exteriors; underlying chat and handoff.md not supplied.</x:v>
+      </x:c>
+      <x:c r="F45" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="48" hidden="0" customHeight="1">
+      <x:c r="A46" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recdQv493Ry8o5y3d</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>Airtable appivZyJTh5tQv1On — Warehouse_Inventory_Observations, session '2026-09-02 — Kees warehouse inventory' (25 observations): goods physically in the DCA warehouse on 2 Sep 2026</x:v>
+      </x:c>
+      <x:c r="C46" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdQv493Ry8o5y3d</x:v>
+      </x:c>
+      <x:c r="D46" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="12" t="str">
+        <x:v>appivZyJTh5tQv1On / tbl6rQmwjUZsrkllO; 25 records WIO-rec6diHrx2DMbh3FC … WIO-recxToaONaYpR72kO created 2026-09-07T00:33–00:34Z; observed_by Kees; record_status current
+Recorded source limit: Approximate counts; no weights; warehouse_location links not read; records entered five days after the session.</x:v>
+      </x:c>
+      <x:c r="F46" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="60" hidden="0" customHeight="1">
+      <x:c r="A47" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recJTH9lXBSM03K14</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>Slack huddle note F0C2F1HL7L1 — Anja–Kees huddle 16 Sep 2026 20:58–21:27 CEST (AI notes): Kees has data from all shipments except two January shipments from Lithuania and one armoured-car shipment [2:20]; method and source-supply agreements</x:v>
+      </x:c>
+      <x:c r="C47" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recJTH9lXBSM03K14</x:v>
+      </x:c>
+      <x:c r="D47" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="12" t="str">
+        <x:v>Slack file F0C2F1HL7L1 (created 2026-09-16 21:28:04 CEST); transcript file F0C2B53A99U (application/vnd.slack-huddle-transcript, 1.2 MB); huddle message https://dcau.slack.com/archives/D0AJR8SJLMQ/p1789585078919509
+Recorded source limit: AI-generated note; the underlying transcript F0C2B53A99U is not readable through this connector (unsupported file type), so timestamps and wording are as summarised.</x:v>
+      </x:c>
+      <x:c r="F47" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="36" hidden="0" customHeight="1">
+      <x:c r="A48" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recdDE2xp8ht4aJ8R</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>Slack #logistics — Bas, 17 Aug 2026 19:18 CEST: full truck to Kharkiv Thu/Fri for €4,600 total (no VAT); DCA ~20 pallets → €2,800; Wilfred fills the rest; another drop-off location before Kyiv (H4U)</x:v>
+      </x:c>
+      <x:c r="C48" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recdDE2xp8ht4aJ8R</x:v>
+      </x:c>
+      <x:c r="D48" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="12" t="str">
+        <x:v>C037X71FME0; message 2026-08-17 19:18:02 CEST (ts not returned by search tool); follow-ups Bas 18 Aug 10:02, James 18 Aug 11:18 (Lena: next week €4,700)
+Recorded source limit: Search-result excerpt truncated; message ts not captured; price is a quote, not an invoice.</x:v>
+      </x:c>
+      <x:c r="F48" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="48" hidden="0" customHeight="1">
+      <x:c r="A49" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recC9dOzCgXbRSQEm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>Slack #logistics — Kees, 21 Aug 2026 08:49 / 13:03 / 16:00 CEST: documents for the truck, loading ~10:00; fully loaded, driver redistributing weight, 'everything is in there'; 'Truck was sent after a long day'</x:v>
+      </x:c>
+      <x:c r="C49" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recC9dOzCgXbRSQEm</x:v>
+      </x:c>
+      <x:c r="D49" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="12" t="str">
+        <x:v>C037X71FME0; messages 2026-08-21 08:49:22, 13:03:12, 16:00:13 CEST (ts not returned by search tool); preceding: Kees 19 Aug 11:02 #marketing 'load a truck tomorrow afternoon or Friday'; Kees 20 Aug 13:48 'Truck will not be able to come today… Likely tomorrow'; James 21 Aug 09:30 asks driver name/passport/phone/plates for declaration
+Recorded source limit: Message ts values not captured; attached documents not enumerated.</x:v>
+      </x:c>
+      <x:c r="F49" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="60" hidden="0" customHeight="1">
+      <x:c r="A50" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recHgOgGg8Rdr638M</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>Slack #logistics — 23–30 Aug 2026: Kees 'expected to arrive on wednesday' (23 Aug); James 'the truck crossed the border yesterday' (24 Aug); Kees 'Truck will be in Kharkiv tomorrow' (25 Aug); Bas 'The truck successfully has been unload it both places' (30 Aug)</x:v>
+      </x:c>
+      <x:c r="C50" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recHgOgGg8Rdr638M</x:v>
+      </x:c>
+      <x:c r="D50" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="12" t="str">
+        <x:v>C037X71FME0; Kees 2026-08-23 08:06:12; James 2026-08-24 10:55:43; Kees 2026-08-25 07:25:36; Bas 2026-08-30 11:05:46 CEST (ts not returned); Reality Watch bot 24 Aug 13:10 (plan Zhytomyr tomorrow, Kharkiv Wednesday) and 29 Aug 08:11 (truck ≠ Mission 39; unloading not yet confirmed) are derivative
+Recorded source limit: Second-hand reports; no consignee receipt, photo or signed CMR processed; Bas's source for the unloading is not stated.</x:v>
+      </x:c>
+      <x:c r="F50" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="60" hidden="0" customHeight="1">
+      <x:c r="A51" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-reclmhgQ3jzfn9gU2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>Slack DM Kees–James — James, 23 Jun 2026 09:16 &amp; 13:30 CEST: 'H4U unloading in Zhytomir, CMR for Help Window as usually. Olga agreed'; sweets → children's camp by New Time, TVs → Lifeline (both Kyiv); Vova unloads in Makariv, truck will not go to Kyiv</x:v>
+      </x:c>
+      <x:c r="C51" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/reclmhgQ3jzfn9gU2</x:v>
+      </x:c>
+      <x:c r="D51" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="12" t="str">
+        <x:v>D0AC3M2J5QE; James 2026-06-23 09:16:04 and 13:30:52 CEST; related James 2026-06-17 10:55:56 ('pallets in Makariv will be downloaded by hands like in Zhytomir by boys… how to unload those tvs so we don't need to send the truck to Kyiv') (ts not returned by search tool)
+Recorded source limit: Instruction before loading; states intended handling, not confirmation of execution; message ts not captured.</x:v>
+      </x:c>
+      <x:c r="F51" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="24" hidden="0" customHeight="1">
+      <x:c r="A52" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recANxlI6i696JKG8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>Slack #logistics — James, 19 May 2026 09:30 CEST: 'Palet number 6 with food for Kamyonka got broken and lose while unloading in HW warehouses… everything was dry'</x:v>
+      </x:c>
+      <x:c r="C52" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recANxlI6i696JKG8</x:v>
+      </x:c>
+      <x:c r="D52" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="12" t="str">
+        <x:v>C037X71FME0; James 2026-05-19 09:30:12 CEST (ts not returned by search tool)
+Recorded source limit: Second-hand report by James; no receipt document; ts not captured.</x:v>
+      </x:c>
+      <x:c r="F52" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="48" hidden="0" customHeight="1">
+      <x:c r="A53" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recxvO3KFoot8GwOE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="6" t="str">
+        <x:v>Slack #logistics — James, 24 Mar 2026 09:34 CEST: recipients 'very happy with the pillows and blankets'; 'with last transport they went through so many hands, that many plastic bags were trash'; send bedding to the organisation unloading first (HW or NR) or to Ludmila</x:v>
+      </x:c>
+      <x:c r="C53" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recxvO3KFoot8GwOE</x:v>
+      </x:c>
+      <x:c r="D53" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="12" t="str">
+        <x:v>C037X71FME0; James 2026-03-24 09:34:50 CEST; follow-up 09:38:55 (request for a Drive folder for loading/unloading photos and videos) (ts not returned by search tool)
+Recorded source limit: Second-hand; 'last transport' presumed to be the 10 Mar truck by date; the unloading media themselves were not located.</x:v>
+      </x:c>
+      <x:c r="F53" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="36" hidden="0" customHeight="1">
+      <x:c r="A54" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recrxfCCX5DKZ9SvY</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="6" t="str">
+        <x:v>Slack group DM Bas/James/Kees — Kees, 6 Jul 2026 17:05 CEST: drivers want lunch with Igor and Olga after unloading at HW warehouse, then drive towards Kyiv; plus Bas 1 Jul #logistics schedule (depart Sat 08:00, overnight Poland, Sunday border) and James 20 Jul price €3,900 + €50 Zhytomyr</x:v>
+      </x:c>
+      <x:c r="C54" s="11" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recrxfCCX5DKZ9SvY</x:v>
+      </x:c>
+      <x:c r="D54" s="12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded; use evidence record/reference</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54" s="12" t="str">
+        <x:v>Group DM: James 2026-07-06 12:23:11 ('prepare for leading them from to 1 unloading and to 2 unloading'); Kees 2026-07-06 17:05:20 CEST. #logistics: Bas 2026-07-01 19:34:58; James 2026-07-20 12:30:32 CEST (ts not returned)
+Recorded source limit: Plans and phone reports; no unloading confirmation document; ts not captured.</x:v>
+      </x:c>
+      <x:c r="F54" s="12" t="str">
+        <x:v>Additional 16 — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="48" hidden="0" customHeight="1">
+      <x:c r="A55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-rectVzwompdkoWvb5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="2" t="str">
+        <x:v>Kees (owner statement, chat 17 Sep 2026): everything sent in May 2026 = the 6 May truck + van mission 36, nothing else; instructs that the May reporting errors be recorded as mistakes to be corrected and that corrected figures be built from the available documents</x:v>
+      </x:c>
+      <x:c r="C55" s="2" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/rectVzwompdkoWvb5</x:v>
+      </x:c>
+      <x:c r="D55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL (chat statement)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E55" s="2" t="str">
+        <x:v>Chat message to Claude, 17 Sep 2026 (no Slack/Gmail permalink; statement made directly in the reconstruction session).
+Recorded source limit: Owner recollection of scope, not a document; James has not been consulted on how his May tab was built, and this statement does not establish his method.</x:v>
+      </x:c>
+      <x:c r="F55" s="2" t="str">
+        <x:v>Later owner/review evidence — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="72" hidden="0" customHeight="1">
+      <x:c r="A56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recsbIRbOrDpPwwWa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="2" t="str">
+        <x:v>Kees (owner) — five comments on the v4 structured output (Google Sheet, 17 Sep 2026 13:44–13:49 UTC): answers to candidate questions Q-E, Q-F, Q-G, Q-I, Q-J</x:v>
+      </x:c>
+      <x:c r="C56" s="2" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recsbIRbOrDpPwwWa</x:v>
+      </x:c>
+      <x:c r="D56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://docs.google.com/spreadsheets/d/12J5c10dLEpiAcW1mOJAOy4NyYZA5osLL_yJ1x2zJfzY/edit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56" s="2" t="str">
+        <x:v>Google Sheet 12J5c10dLEpiAcW1mOJAOy4NyYZA5osLL_yJ1x2zJfzY; comment IDs AAACHP_qrIs (C7), AAACHP_qrIw (C8), AAACHP_qrI0 (C9), AAACHP_qrI4 (C11), AAACHP_qrI8 (C12); all status OPEN; modified 2026-09-17T13:44–13:49Z.
+Recorded source limit: Owner statements, not documents. Q-F is explicitly '99% sure', i.e. a strong assessment, not a record. Comments were left on a copy of the v4 export uploaded to Drive by Kees; they are not replies in a validation thread and no other reviewer has responded.</x:v>
+      </x:c>
+      <x:c r="F56" s="2" t="str">
+        <x:v>Later owner/review evidence — incorporated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="48" hidden="0" customHeight="1">
+      <x:c r="A57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EVD-recoHTWw0w5oqPDCT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="2" t="str">
+        <x:v>Slack #marketing — James &amp; Bas, 13–16 Mar 2026: five ambulances repaired with DCA participation (€2,000 repair + €500 transport each per Bas); one prepared for Bogdan's evacuation team in Kramatorsk; 'The ambulances will go to Ukraine at the end of March'</x:v>
+      </x:c>
+      <x:c r="C57" s="2" t="str">
+        <x:v>https://airtable.com/appZ1Fv0YtZPbBbWa/tbl35kxZNyfhKmtXG/recoHTWw0w5oqPDCT</x:v>
+      </x:c>
+      <x:c r="D57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">No direct URL recorded</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57" s="2" t="str">
+        <x:v>Slack C037S4YL6MT; James 2026-03-13 14:51:54, Bas 14:55:07 and 14:58:40, lieke 19:44:53; lieke 2026-03-16 10:36:02, James 11:51:29 CET (ts values not returned by the search tool).
+Recorded source limit: Marketing-channel statements; € figures are Bas's understanding posed as a question; whether/when ambulances physically went, and whether vehicles are 'goods' for reporting, is not established.</x:v>
+      </x:c>
+      <x:c r="F57" s="2" t="str">
+        <x:v>Later owner/review evidence — incorporated</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
